--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -387,7 +387,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -753,6 +753,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1821,7 +1824,7 @@
         </is>
       </c>
       <c r="C1" s="12" t="n">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="D1" s="12" t="inlineStr">
         <is>
@@ -1913,28 +1916,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="100" t="n">
-        <v>8365729.168039998</v>
+        <v>19084602.17775</v>
       </c>
       <c r="E6" s="101">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="100" t="n">
-        <v>7888941.65873</v>
+        <v>18525484.71198</v>
       </c>
       <c r="G6" s="101">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="100" t="n">
-        <v>9230830.973002382</v>
+        <v>20769369.68925536</v>
       </c>
       <c r="I6" s="101">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="100" t="n">
-        <v>9200000</v>
+        <v>20100000</v>
       </c>
       <c r="K6" s="101">
         <f>D6/J6</f>
@@ -1952,28 +1955,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="100" t="n">
-        <v>11186465.20426</v>
+        <v>25946622.54581</v>
       </c>
       <c r="E7" s="101">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="100" t="n">
-        <v>13256328.96626</v>
+        <v>31373937.66763</v>
       </c>
       <c r="G7" s="101">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="100" t="n">
-        <v>16967966.69595202</v>
+        <v>38177925.06589205</v>
       </c>
       <c r="I7" s="101">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="100" t="n">
-        <v>16627604</v>
+        <v>39352010.8</v>
       </c>
       <c r="K7" s="101">
         <f>D7/J7</f>
@@ -1991,28 +1994,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="100" t="n">
-        <v>1377541.48113</v>
+        <v>3286944.35109</v>
       </c>
       <c r="E8" s="101">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="100" t="n">
-        <v>833421.4057400001</v>
+        <v>2232121.1192</v>
       </c>
       <c r="G8" s="101">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="100" t="n">
-        <v>1213083.387371968</v>
+        <v>2729437.621586928</v>
       </c>
       <c r="I8" s="101">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="100" t="n">
-        <v>1320000</v>
+        <v>2860000</v>
       </c>
       <c r="K8" s="101">
         <f>D8/J8</f>
@@ -2030,28 +2033,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="100" t="n">
-        <v>10031145.92848</v>
+        <v>20892242.00753</v>
       </c>
       <c r="E9" s="101">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="100" t="n">
-        <v>9086020.86906</v>
+        <v>19760858.74571</v>
       </c>
       <c r="G9" s="101">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="100" t="n">
-        <v>11311977.79730134</v>
+        <v>25451950.04392803</v>
       </c>
       <c r="I9" s="101">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="100" t="n">
-        <v>9571860</v>
+        <v>22117293</v>
       </c>
       <c r="K9" s="101">
         <f>D9/J9</f>
@@ -2069,28 +2072,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="100" t="n">
-        <v>6985790.939379999</v>
+        <v>16481174.63984</v>
       </c>
       <c r="E10" s="101">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="100" t="n">
-        <v>7129930.010129999</v>
+        <v>14542584.69997</v>
       </c>
       <c r="G10" s="101">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="100" t="n">
-        <v>8483983.347976008</v>
+        <v>19088962.53294602</v>
       </c>
       <c r="I10" s="101">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="100" t="n">
-        <v>7900000</v>
+        <v>18600000</v>
       </c>
       <c r="K10" s="101">
         <f>D10/J10</f>
@@ -2108,28 +2111,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="100" t="n">
-        <v>6050136.903990002</v>
+        <v>13101116.62298</v>
       </c>
       <c r="E11" s="101">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="100" t="n">
-        <v>6406642.700529999</v>
+        <v>15038979.16497999</v>
       </c>
       <c r="G11" s="101">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="100" t="n">
-        <v>8020037.618408356</v>
+        <v>18045084.6414188</v>
       </c>
       <c r="I11" s="101">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="100" t="n">
-        <v>7896160.52</v>
+        <v>17316176.26</v>
       </c>
       <c r="K11" s="101">
         <f>D11/J11</f>
@@ -3976,40 +3979,40 @@
         </is>
       </c>
       <c r="C45" s="104" t="n">
-        <v>116.50956</v>
+        <v>112.237713786</v>
       </c>
       <c r="D45" s="105" t="n">
-        <v>120</v>
+        <v>115.634</v>
       </c>
       <c r="E45" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.970913</v>
+        <v>0.970629</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.029087</v>
+        <v>0.029371</v>
       </c>
       <c r="H45" s="101" t="n">
-        <v>0.794098</v>
+        <v>0.798925</v>
       </c>
       <c r="I45" s="101" t="n">
-        <v>0.838179</v>
+        <v>0.826742</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>-4.4081</v>
+        <v>-2.7817</v>
       </c>
       <c r="K45" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L45" s="101" t="n">
-        <v>0.993905</v>
+        <v>0.993004</v>
       </c>
       <c r="M45" s="101" t="n">
-        <v>0.8688789999999998</v>
+        <v>0.8574419999999999</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>12.50260000000002</v>
+        <v>13.5562</v>
       </c>
       <c r="O45" s="15" t="n">
         <v>-2</v>
@@ -4032,31 +4035,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.395096</v>
+        <v>0.528797</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0.604904</v>
+        <v>0.471203</v>
       </c>
       <c r="H46" s="101" t="n">
-        <v>0.865675</v>
+        <v>0.89567</v>
       </c>
       <c r="I46" s="101" t="n">
-        <v>0.86239</v>
+        <v>0.866765</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>0.3285</v>
+        <v>2.8905</v>
       </c>
       <c r="K46" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="101" t="n">
-        <v>0.95884</v>
+        <v>0.954748</v>
       </c>
       <c r="M46" s="101" t="n">
-        <v>0.8930899999999999</v>
+        <v>0.897465</v>
       </c>
       <c r="N46" s="15" t="n">
-        <v>6.575000000000003</v>
+        <v>5.728300000000004</v>
       </c>
       <c r="O46" s="15" t="n">
         <v>-2</v>
@@ -4070,40 +4073,40 @@
         </is>
       </c>
       <c r="C47" s="104" t="n">
-        <v>0</v>
+        <v>103.608822464</v>
       </c>
       <c r="D47" s="105" t="n">
-        <v>0</v>
+        <v>106.758</v>
       </c>
       <c r="E47" s="105" t="n">
-        <v>0</v>
+        <v>64.89399999999989</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.923305</v>
+        <v>0.924776</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.076695</v>
+        <v>0.075224</v>
       </c>
       <c r="H47" s="101" t="n">
-        <v>0.78331</v>
+        <v>0.7618509999999999</v>
       </c>
       <c r="I47" s="101" t="n">
-        <v>0.774099</v>
+        <v>0.78523</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0.9211</v>
+        <v>-2.3379</v>
       </c>
       <c r="K47" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="101" t="n">
-        <v>0.911517</v>
+        <v>0.813483</v>
       </c>
       <c r="M47" s="101" t="n">
-        <v>0.8047989999999998</v>
+        <v>0.8159299999999999</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>10.67180000000002</v>
+        <v>-0.2446999999999946</v>
       </c>
       <c r="O47" s="15" t="n">
         <v>-2</v>
@@ -4117,40 +4120,40 @@
         </is>
       </c>
       <c r="C48" s="104" t="n">
-        <v>96.852090984</v>
+        <v>81.018992184</v>
       </c>
       <c r="D48" s="105" t="n">
-        <v>108.658</v>
+        <v>92.696</v>
       </c>
       <c r="E48" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.891348</v>
+        <v>0.8740289999999999</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.108652</v>
+        <v>0.125971</v>
       </c>
       <c r="H48" s="101" t="n">
-        <v>0.805346</v>
+        <v>0.812965</v>
       </c>
       <c r="I48" s="101" t="n">
-        <v>0.8296750000000001</v>
+        <v>0.829313</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>-2.4329</v>
+        <v>-1.6348</v>
       </c>
       <c r="K48" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="101" t="n">
-        <v>0.89014</v>
+        <v>0.883899</v>
       </c>
       <c r="M48" s="101" t="n">
-        <v>0.8603749999999999</v>
+        <v>0.8600129999999999</v>
       </c>
       <c r="N48" s="15" t="n">
-        <v>2.976500000000001</v>
+        <v>2.388600000000011</v>
       </c>
       <c r="O48" s="15" t="n">
         <v>-2</v>
@@ -4173,31 +4176,31 @@
         <v>0</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.8452229999999999</v>
+        <v>0.824055</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.154777</v>
+        <v>0.175945</v>
       </c>
       <c r="H49" s="101" t="n">
-        <v>0.891162</v>
+        <v>0.890191</v>
       </c>
       <c r="I49" s="101" t="n">
-        <v>0.826307</v>
+        <v>0.831803</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>6.4855</v>
+        <v>5.8388</v>
       </c>
       <c r="K49" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="101" t="n">
-        <v>0.89959</v>
+        <v>0.889737</v>
       </c>
       <c r="M49" s="101" t="n">
-        <v>0.857007</v>
+        <v>0.8625029999999999</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>4.258300000000006</v>
+        <v>2.723399999999998</v>
       </c>
       <c r="O49" s="15" t="n">
         <v>-2</v>
@@ -4210,43 +4213,31 @@
           <t>海淘组</t>
         </is>
       </c>
-      <c r="C50" s="104" t="inlineStr">
+      <c r="C50" s="104" t="n">
+        <v>120</v>
+      </c>
+      <c r="D50" s="105" t="n">
+        <v>120</v>
+      </c>
+      <c r="E50" s="105" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
       </c>
-      <c r="D50" s="105" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="E50" s="105" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="H50" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="101" t="n">
+        <v>0.7324040000000001</v>
       </c>
       <c r="I50" s="101" t="n">
-        <v>0.842755</v>
-      </c>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
+        <v>0.852545</v>
+      </c>
+      <c r="J50" s="15" t="n">
+        <v>-12.0141</v>
       </c>
       <c r="K50" s="106" t="n">
         <v>-2</v>
@@ -4257,7 +4248,7 @@
         </is>
       </c>
       <c r="M50" s="101" t="n">
-        <v>0.8734549999999999</v>
+        <v>0.8832449999999998</v>
       </c>
       <c r="N50" s="15" t="inlineStr">
         <is>
@@ -7484,70 +7475,50 @@
           <t>小组</t>
         </is>
       </c>
-      <c r="C79" s="83" t="inlineStr">
-        <is>
-          <t>日均6高商品数</t>
-        </is>
-      </c>
-      <c r="D79" s="83" t="inlineStr">
-        <is>
-          <t>可比率</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>天猫价格指数</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>天猫价指目标</t>
-        </is>
+      <c r="C79" s="83" t="n">
+        <v>1451.555555555556</v>
+      </c>
+      <c r="D79" s="83" t="n">
+        <v>0.702924066135946</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>0.898787</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>0.8146325152</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
           <t>vs天猫目标</t>
         </is>
       </c>
-      <c r="H79" s="83" t="inlineStr">
-        <is>
-          <t>抖音价格指数</t>
-        </is>
-      </c>
-      <c r="I79" s="83" t="inlineStr">
-        <is>
-          <t>抖音价指目标</t>
-        </is>
+      <c r="H79" s="83" t="n">
+        <v>0.893788</v>
+      </c>
+      <c r="I79" s="83" t="n">
+        <v>0.8207995184</v>
       </c>
       <c r="J79" s="83" t="inlineStr">
         <is>
           <t>vs抖音目标</t>
         </is>
       </c>
-      <c r="K79" s="13" t="inlineStr">
-        <is>
-          <t>调价率</t>
-        </is>
-      </c>
-      <c r="L79" s="13" t="inlineStr">
-        <is>
-          <t>调价率目标</t>
-        </is>
+      <c r="K79" s="13" t="n">
+        <v>0.7766497461928934</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>0.8082191781</v>
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
           <t>vs目标</t>
         </is>
       </c>
-      <c r="N79" s="83" t="inlineStr">
-        <is>
-          <t>整体断货率</t>
-        </is>
-      </c>
-      <c r="O79" s="83" t="inlineStr">
-        <is>
-          <t>断货率目标</t>
-        </is>
+      <c r="N79" s="83" t="n">
+        <v>0.0637602006795161</v>
+      </c>
+      <c r="O79" s="83" t="n">
+        <v>0.0611152139</v>
       </c>
       <c r="P79" s="83" t="inlineStr">
         <is>
@@ -7562,22 +7533,24 @@
         </is>
       </c>
       <c r="C80" s="19" t="n">
-        <v>1453</v>
+        <v>111.8888888888889</v>
       </c>
       <c r="D80" s="101" t="n">
-        <v>0.700963523743978</v>
+        <v>0.2442899702085402</v>
       </c>
       <c r="E80" s="101" t="n">
-        <v>0.903735</v>
+        <v>0.7324040000000001</v>
       </c>
       <c r="F80" s="101" t="n">
-        <v>0.8146325152</v>
+        <v>0.7556221149</v>
       </c>
       <c r="G80" s="101" t="n">
         <v>0.1383624848</v>
       </c>
-      <c r="H80" s="101" t="n">
-        <v>0.912928</v>
+      <c r="H80" s="101" t="inlineStr">
+        <is>
+          <t>(NULL)</t>
+        </is>
       </c>
       <c r="I80" s="101" t="n">
         <v>0.8207995184</v>
@@ -7586,7 +7559,7 @@
         <v>0.1598504816</v>
       </c>
       <c r="K80" s="101" t="n">
-        <v>0.752212389380531</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="101" t="n">
         <v>0.8082191781</v>
@@ -7595,7 +7568,7 @@
         <v>-0.1240086517842105</v>
       </c>
       <c r="N80" s="101" t="n">
-        <v>0.0669070037710789</v>
+        <v>0.1676190476190476</v>
       </c>
       <c r="O80" s="101" t="n">
         <v>0.0611152139</v>
@@ -7611,28 +7584,24 @@
         </is>
       </c>
       <c r="C81" s="19" t="n">
-        <v>110.75</v>
+        <v>354.3333333333333</v>
       </c>
       <c r="D81" s="101" t="n">
-        <v>0.2212189616252822</v>
-      </c>
-      <c r="E81" s="101" t="inlineStr">
+        <v>0.7184070241455002</v>
+      </c>
+      <c r="E81" s="101" t="n">
+        <v>0.88931</v>
+      </c>
+      <c r="F81" s="101" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="G81" s="101" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
       </c>
-      <c r="F81" s="101" t="n">
-        <v>0.7556221149</v>
-      </c>
-      <c r="G81" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="H81" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
+      <c r="H81" s="101" t="n">
+        <v>0.893321</v>
       </c>
       <c r="I81" s="101" t="n">
         <v>0.8207995184</v>
@@ -7643,7 +7612,7 @@
         </is>
       </c>
       <c r="K81" s="101" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L81" s="101" t="n">
         <v>0.8082191781</v>
@@ -7652,7 +7621,7 @@
         <v>-0.8082191781</v>
       </c>
       <c r="N81" s="101" t="n">
-        <v>0.2</v>
+        <v>0.0540330417881438</v>
       </c>
       <c r="O81" s="101" t="n">
         <v>0.0611152139</v>
@@ -7668,22 +7637,22 @@
         </is>
       </c>
       <c r="C82" s="19" t="n">
-        <v>357.25</v>
+        <v>887.3333333333334</v>
       </c>
       <c r="D82" s="101" t="n">
-        <v>0.7123862841147656</v>
+        <v>0.7910092662158777</v>
       </c>
       <c r="E82" s="101" t="n">
-        <v>0.897056</v>
+        <v>0.917654</v>
       </c>
       <c r="F82" s="101" t="n">
-        <v>0.8066</v>
+        <v>0.8078</v>
       </c>
       <c r="G82" s="101" t="n">
         <v>0.15917</v>
       </c>
       <c r="H82" s="101" t="n">
-        <v>0.914577</v>
+        <v>0.895008</v>
       </c>
       <c r="I82" s="101" t="n">
         <v>0.8207995184</v>
@@ -7692,7 +7661,7 @@
         <v>0.1714954816000001</v>
       </c>
       <c r="K82" s="101" t="n">
-        <v>1</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="L82" s="101" t="n">
         <v>0.8082191781</v>
@@ -7701,7 +7670,7 @@
         <v>0.1917808219</v>
       </c>
       <c r="N82" s="101" t="n">
-        <v>0.0491341991341991</v>
+        <v>0.06928811094031501</v>
       </c>
       <c r="O82" s="101" t="n">
         <v>0.0611152139</v>
@@ -7717,22 +7686,24 @@
         </is>
       </c>
       <c r="C83" s="19" t="n">
-        <v>887</v>
+        <v>1</v>
       </c>
       <c r="D83" s="101" t="n">
-        <v>0.7919954904171363</v>
-      </c>
-      <c r="E83" s="101" t="n">
-        <v>0.917624</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E83" s="101" t="inlineStr">
+        <is>
+          <t>(NULL)</t>
+        </is>
       </c>
       <c r="F83" s="101" t="n">
-        <v>0.8078</v>
+        <v>0.8417108422</v>
       </c>
       <c r="G83" s="101" t="n">
         <v>0.125283</v>
       </c>
       <c r="H83" s="101" t="n">
-        <v>0.902262</v>
+        <v>1</v>
       </c>
       <c r="I83" s="101" t="n">
         <v>0.8207995184</v>
@@ -7740,8 +7711,10 @@
       <c r="J83" s="101" t="n">
         <v>0.09684448160000003</v>
       </c>
-      <c r="K83" s="101" t="n">
-        <v>0.7378640776699029</v>
+      <c r="K83" s="101" t="inlineStr">
+        <is>
+          <t>(NULL)</t>
+        </is>
       </c>
       <c r="L83" s="101" t="n">
         <v>0.8082191781</v>
@@ -7750,7 +7723,7 @@
         <v>-0.1317485898647059</v>
       </c>
       <c r="N83" s="101" t="n">
-        <v>0.0764988897113249</v>
+        <v>0</v>
       </c>
       <c r="O83" s="101" t="n">
         <v>0.0611152139</v>
@@ -7766,10 +7739,10 @@
         </is>
       </c>
       <c r="C84" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" s="101" t="n">
-        <v>0.5</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="E84" s="101" t="inlineStr">
         <is>
@@ -7777,15 +7750,17 @@
         </is>
       </c>
       <c r="F84" s="101" t="n">
-        <v>0.8417108422</v>
+        <v>0.7771375317</v>
       </c>
       <c r="G84" s="101" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
       </c>
-      <c r="H84" s="101" t="n">
-        <v>1</v>
+      <c r="H84" s="101" t="inlineStr">
+        <is>
+          <t>(NULL)</t>
+        </is>
       </c>
       <c r="I84" s="101" t="n">
         <v>0.8207995184</v>
@@ -7809,7 +7784,7 @@
         </is>
       </c>
       <c r="N84" s="101" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="O84" s="101" t="n">
         <v>0.0611152139</v>
@@ -7825,28 +7800,24 @@
         </is>
       </c>
       <c r="C85" s="19" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="D85" s="101" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E85" s="101" t="inlineStr">
+        <v>0.3637426900584795</v>
+      </c>
+      <c r="E85" s="101" t="n">
+        <v>0.850256</v>
+      </c>
+      <c r="F85" s="101" t="n">
+        <v>0.8087257009</v>
+      </c>
+      <c r="G85" s="101" t="inlineStr">
         <is>
           <t>(NULL)</t>
         </is>
       </c>
-      <c r="F85" s="101" t="n">
-        <v>0.7771375317</v>
-      </c>
-      <c r="G85" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
-      </c>
-      <c r="H85" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
+      <c r="H85" s="101" t="n">
+        <v>0.803268</v>
       </c>
       <c r="I85" s="101" t="n">
         <v>0.8207995184</v>
@@ -7870,7 +7841,7 @@
         </is>
       </c>
       <c r="N85" s="101" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.0226214238190286</v>
       </c>
       <c r="O85" s="101" t="n">
         <v>0.0611152139</v>
@@ -7952,20 +7923,14 @@
           <t>小组</t>
         </is>
       </c>
-      <c r="C91" s="83" t="inlineStr">
-        <is>
-          <t>已引进</t>
-        </is>
-      </c>
-      <c r="D91" s="83" t="inlineStr">
-        <is>
-          <t>未引入</t>
-        </is>
-      </c>
-      <c r="E91" s="83" t="inlineStr">
-        <is>
-          <t>暂不引进</t>
-        </is>
+      <c r="C91" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="83" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="83" t="inlineStr">
         <is>
@@ -7988,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5" t="n">
         <v>0</v>
@@ -8012,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0</v>
@@ -8036,7 +8001,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0</v>
@@ -10325,25 +10290,19 @@
     </row>
     <row r="132" ht="13.5" customHeight="1">
       <c r="B132" s="84" t="n"/>
-      <c r="C132" s="95" t="inlineStr">
-        <is>
-          <t>曝光</t>
-        </is>
-      </c>
-      <c r="D132" s="95" t="inlineStr">
-        <is>
-          <t>APP销售</t>
-        </is>
+      <c r="C132" s="95" t="n">
+        <v>0.1996959750892681</v>
+      </c>
+      <c r="D132" s="95" t="n">
+        <v>0.319269</v>
       </c>
       <c r="E132" s="85" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="F132" s="85" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
+      <c r="F132" s="85" t="n">
+        <v>2.037636278655495</v>
       </c>
       <c r="G132" s="85" t="inlineStr">
         <is>
@@ -10355,15 +10314,11 @@
           <t>完成率</t>
         </is>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>曝光</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>APP销售</t>
-        </is>
+      <c r="I132" s="1" t="n">
+        <v>7407967.666666667</v>
+      </c>
+      <c r="J132" s="1" t="n">
+        <v>1369228.307039</v>
       </c>
     </row>
     <row r="133">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C1" s="12" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="D1" s="12" t="inlineStr">
         <is>
@@ -1916,28 +1916,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="100" t="n">
-        <v>19084602.17775</v>
+        <v>26229219.03465001</v>
       </c>
       <c r="E6" s="101">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="100" t="n">
-        <v>18525484.71198</v>
+        <v>25198952.36185999</v>
       </c>
       <c r="G6" s="101">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="100" t="n">
-        <v>20769369.68925536</v>
+        <v>28515941.75414003</v>
       </c>
       <c r="I6" s="101">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="100" t="n">
-        <v>20100000</v>
+        <v>27900000</v>
       </c>
       <c r="K6" s="101">
         <f>D6/J6</f>
@@ -1955,28 +1955,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="100" t="n">
-        <v>25946622.54581</v>
+        <v>36650853.98930001</v>
       </c>
       <c r="E7" s="101">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="100" t="n">
-        <v>31373937.66763</v>
+        <v>42700003.63986</v>
       </c>
       <c r="G7" s="101">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="100" t="n">
-        <v>38177925.06589205</v>
+        <v>52417550.64122663</v>
       </c>
       <c r="I7" s="101">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="100" t="n">
-        <v>39352010.8</v>
+        <v>53561034.7</v>
       </c>
       <c r="K7" s="101">
         <f>D7/J7</f>
@@ -1994,28 +1994,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="100" t="n">
-        <v>3286944.35109</v>
+        <v>5001488.85697</v>
       </c>
       <c r="E8" s="101">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="100" t="n">
-        <v>2232121.1192</v>
+        <v>3061055.493069999</v>
       </c>
       <c r="G8" s="101">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="100" t="n">
-        <v>2729437.621586928</v>
+        <v>3747464.916039146</v>
       </c>
       <c r="I8" s="101">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="100" t="n">
-        <v>2860000</v>
+        <v>3917018.15389968</v>
       </c>
       <c r="K8" s="101">
         <f>D8/J8</f>
@@ -2033,28 +2033,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="100" t="n">
-        <v>20892242.00753</v>
+        <v>29396598.11794</v>
       </c>
       <c r="E9" s="101">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="100" t="n">
-        <v>19760858.74571</v>
+        <v>28718076.21583001</v>
       </c>
       <c r="G9" s="101">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="100" t="n">
-        <v>25451950.04392803</v>
+        <v>34945033.76081775</v>
       </c>
       <c r="I9" s="101">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="100" t="n">
-        <v>22117293</v>
+        <v>31909566</v>
       </c>
       <c r="K9" s="101">
         <f>D9/J9</f>
@@ -2072,28 +2072,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="100" t="n">
-        <v>16481174.63984</v>
+        <v>24001794.60806</v>
       </c>
       <c r="E10" s="101">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="100" t="n">
-        <v>14542584.69997</v>
+        <v>23336710.93771</v>
       </c>
       <c r="G10" s="101">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="100" t="n">
-        <v>19088962.53294602</v>
+        <v>26208775.32061331</v>
       </c>
       <c r="I10" s="101">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="100" t="n">
-        <v>18600000</v>
+        <v>27200000</v>
       </c>
       <c r="K10" s="101">
         <f>D10/J10</f>
@@ -2111,28 +2111,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="100" t="n">
-        <v>13101116.62298</v>
+        <v>18107267.64684</v>
       </c>
       <c r="E11" s="101">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="100" t="n">
-        <v>15038979.16497999</v>
+        <v>20723865.86578</v>
       </c>
       <c r="G11" s="101">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="100" t="n">
-        <v>18045084.6414188</v>
+        <v>24775551.22192417</v>
       </c>
       <c r="I11" s="101">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="100" t="n">
-        <v>17316176.26</v>
+        <v>25300548.09</v>
       </c>
       <c r="K11" s="101">
         <f>D11/J11</f>
@@ -3979,40 +3979,40 @@
         </is>
       </c>
       <c r="C45" s="104" t="n">
-        <v>112.237713786</v>
+        <v>113.993424552</v>
       </c>
       <c r="D45" s="105" t="n">
-        <v>115.634</v>
+        <v>117.112</v>
       </c>
       <c r="E45" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.970629</v>
+        <v>0.973371</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.029371</v>
+        <v>0.026629</v>
       </c>
       <c r="H45" s="101" t="n">
-        <v>0.798925</v>
+        <v>0.795024</v>
       </c>
       <c r="I45" s="101" t="n">
-        <v>0.826742</v>
+        <v>0.82358</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>-2.7817</v>
+        <v>-2.8556</v>
       </c>
       <c r="K45" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L45" s="101" t="n">
-        <v>0.993004</v>
+        <v>0.992406</v>
       </c>
       <c r="M45" s="101" t="n">
-        <v>0.8574419999999999</v>
+        <v>0.8542799999999999</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>13.5562</v>
+        <v>13.8126</v>
       </c>
       <c r="O45" s="15" t="n">
         <v>-2</v>
@@ -4035,31 +4035,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.528797</v>
+        <v>0.531453</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0.471203</v>
+        <v>0.468547</v>
       </c>
       <c r="H46" s="101" t="n">
-        <v>0.89567</v>
+        <v>0.8861830000000001</v>
       </c>
       <c r="I46" s="101" t="n">
-        <v>0.866765</v>
+        <v>0.861343</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>2.8905</v>
+        <v>2.484</v>
       </c>
       <c r="K46" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="101" t="n">
-        <v>0.954748</v>
+        <v>0.949923</v>
       </c>
       <c r="M46" s="101" t="n">
-        <v>0.897465</v>
+        <v>0.8920429999999999</v>
       </c>
       <c r="N46" s="15" t="n">
-        <v>5.728300000000004</v>
+        <v>5.788000000000011</v>
       </c>
       <c r="O46" s="15" t="n">
         <v>-2</v>
@@ -4073,40 +4073,40 @@
         </is>
       </c>
       <c r="C47" s="104" t="n">
-        <v>103.608822464</v>
+        <v>120</v>
       </c>
       <c r="D47" s="105" t="n">
-        <v>106.758</v>
+        <v>120</v>
       </c>
       <c r="E47" s="105" t="n">
-        <v>64.89399999999989</v>
+        <v>120</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.924776</v>
+        <v>0.919815</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.075224</v>
+        <v>0.08018500000000001</v>
       </c>
       <c r="H47" s="101" t="n">
-        <v>0.7618509999999999</v>
+        <v>0.755246</v>
       </c>
       <c r="I47" s="101" t="n">
-        <v>0.78523</v>
+        <v>0.788981</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>-2.3379</v>
+        <v>-3.3735</v>
       </c>
       <c r="K47" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="101" t="n">
-        <v>0.813483</v>
+        <v>0.77584</v>
       </c>
       <c r="M47" s="101" t="n">
-        <v>0.8159299999999999</v>
+        <v>0.8196809999999999</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>-0.2446999999999946</v>
+        <v>-4.384099999999989</v>
       </c>
       <c r="O47" s="15" t="n">
         <v>-2</v>
@@ -4120,40 +4120,40 @@
         </is>
       </c>
       <c r="C48" s="104" t="n">
-        <v>81.018992184</v>
+        <v>78.170427864</v>
       </c>
       <c r="D48" s="105" t="n">
-        <v>92.696</v>
+        <v>89.514</v>
       </c>
       <c r="E48" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.8740289999999999</v>
+        <v>0.8732760000000001</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.125971</v>
+        <v>0.126724</v>
       </c>
       <c r="H48" s="101" t="n">
-        <v>0.812965</v>
+        <v>0.812524</v>
       </c>
       <c r="I48" s="101" t="n">
-        <v>0.829313</v>
+        <v>0.827281</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>-1.6348</v>
+        <v>-1.4757</v>
       </c>
       <c r="K48" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="101" t="n">
-        <v>0.883899</v>
+        <v>0.876089</v>
       </c>
       <c r="M48" s="101" t="n">
-        <v>0.8600129999999999</v>
+        <v>0.8579809999999999</v>
       </c>
       <c r="N48" s="15" t="n">
-        <v>2.388600000000011</v>
+        <v>1.810800000000015</v>
       </c>
       <c r="O48" s="15" t="n">
         <v>-2</v>
@@ -4176,31 +4176,31 @@
         <v>0</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.824055</v>
+        <v>0.82184</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.175945</v>
+        <v>0.17816</v>
       </c>
       <c r="H49" s="101" t="n">
-        <v>0.890191</v>
+        <v>0.885202</v>
       </c>
       <c r="I49" s="101" t="n">
-        <v>0.831803</v>
+        <v>0.83172</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>5.8388</v>
+        <v>5.3482</v>
       </c>
       <c r="K49" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="101" t="n">
-        <v>0.889737</v>
+        <v>0.885636</v>
       </c>
       <c r="M49" s="101" t="n">
-        <v>0.8625029999999999</v>
+        <v>0.8624199999999999</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>2.723399999999998</v>
+        <v>2.321600000000004</v>
       </c>
       <c r="O49" s="15" t="n">
         <v>-2</v>
@@ -4231,13 +4231,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="101" t="n">
-        <v>0.7324040000000001</v>
+        <v>0.725952</v>
       </c>
       <c r="I50" s="101" t="n">
-        <v>0.852545</v>
+        <v>0.851125</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>-12.0141</v>
+        <v>-12.5173</v>
       </c>
       <c r="K50" s="106" t="n">
         <v>-2</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="M50" s="101" t="n">
-        <v>0.8832449999999998</v>
+        <v>0.8818249999999999</v>
       </c>
       <c r="N50" s="15" t="inlineStr">
         <is>
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="C79" s="83" t="n">
-        <v>1451.555555555556</v>
+        <v>1438.333333333333</v>
       </c>
       <c r="D79" s="83" t="n">
-        <v>0.702924066135946</v>
+        <v>0.7069524913093859</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>0.898787</v>
+        <v>0.892247</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>0.8146325152</v>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="H79" s="83" t="n">
-        <v>0.893788</v>
+        <v>0.8853529999999999</v>
       </c>
       <c r="I79" s="83" t="n">
         <v>0.8207995184</v>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0.7766497461928934</v>
+        <v>0.7703349282296651</v>
       </c>
       <c r="L79" s="13" t="n">
         <v>0.8082191781</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="N79" s="83" t="n">
-        <v>0.0637602006795161</v>
+        <v>0.0641322366998486</v>
       </c>
       <c r="O79" s="83" t="n">
         <v>0.0611152139</v>
@@ -7533,13 +7533,13 @@
         </is>
       </c>
       <c r="C80" s="19" t="n">
-        <v>111.8888888888889</v>
+        <v>112.5</v>
       </c>
       <c r="D80" s="101" t="n">
-        <v>0.2442899702085402</v>
+        <v>0.2422222222222222</v>
       </c>
       <c r="E80" s="101" t="n">
-        <v>0.7324040000000001</v>
+        <v>0.725952</v>
       </c>
       <c r="F80" s="101" t="n">
         <v>0.7556221149</v>
@@ -7568,7 +7568,7 @@
         <v>-0.1240086517842105</v>
       </c>
       <c r="N80" s="101" t="n">
-        <v>0.1676190476190476</v>
+        <v>0.1621621621621622</v>
       </c>
       <c r="O80" s="101" t="n">
         <v>0.0611152139</v>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="C81" s="19" t="n">
-        <v>354.3333333333333</v>
+        <v>343.5833333333333</v>
       </c>
       <c r="D81" s="101" t="n">
-        <v>0.7184070241455002</v>
+        <v>0.7184089255396556</v>
       </c>
       <c r="E81" s="101" t="n">
-        <v>0.88931</v>
+        <v>0.883168</v>
       </c>
       <c r="F81" s="101" t="n">
         <v>0.8066</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="H81" s="101" t="n">
-        <v>0.893321</v>
+        <v>0.8847429999999999</v>
       </c>
       <c r="I81" s="101" t="n">
         <v>0.8207995184</v>
@@ -7621,7 +7621,7 @@
         <v>-0.8082191781</v>
       </c>
       <c r="N81" s="101" t="n">
-        <v>0.0540330417881438</v>
+        <v>0.055196513113399</v>
       </c>
       <c r="O81" s="101" t="n">
         <v>0.0611152139</v>
@@ -7637,13 +7637,13 @@
         </is>
       </c>
       <c r="C82" s="19" t="n">
-        <v>887.3333333333334</v>
+        <v>884.0833333333334</v>
       </c>
       <c r="D82" s="101" t="n">
-        <v>0.7910092662158777</v>
+        <v>0.7984729946272033</v>
       </c>
       <c r="E82" s="101" t="n">
-        <v>0.917654</v>
+        <v>0.909911</v>
       </c>
       <c r="F82" s="101" t="n">
         <v>0.8078</v>
@@ -7652,7 +7652,7 @@
         <v>0.15917</v>
       </c>
       <c r="H82" s="101" t="n">
-        <v>0.895008</v>
+        <v>0.887755</v>
       </c>
       <c r="I82" s="101" t="n">
         <v>0.8207995184</v>
@@ -7661,7 +7661,7 @@
         <v>0.1714954816000001</v>
       </c>
       <c r="K82" s="101" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.7459459459459459</v>
       </c>
       <c r="L82" s="101" t="n">
         <v>0.8082191781</v>
@@ -7670,7 +7670,7 @@
         <v>0.1917808219</v>
       </c>
       <c r="N82" s="101" t="n">
-        <v>0.06928811094031501</v>
+        <v>0.0700038573046151</v>
       </c>
       <c r="O82" s="101" t="n">
         <v>0.0611152139</v>
@@ -7689,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="101" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8</v>
       </c>
       <c r="E83" s="101" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>0.125283</v>
       </c>
       <c r="H83" s="101" t="n">
-        <v>1</v>
+        <v>0.999768</v>
       </c>
       <c r="I83" s="101" t="n">
         <v>0.8207995184</v>
@@ -7742,7 +7742,7 @@
         <v>2</v>
       </c>
       <c r="D84" s="101" t="n">
-        <v>0.611111111111111</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E84" s="101" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="N84" s="101" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.25</v>
       </c>
       <c r="O84" s="101" t="n">
         <v>0.0611152139</v>
@@ -7800,13 +7800,13 @@
         </is>
       </c>
       <c r="C85" s="19" t="n">
-        <v>95</v>
+        <v>95.33333333333333</v>
       </c>
       <c r="D85" s="101" t="n">
-        <v>0.3637426900584795</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="E85" s="101" t="n">
-        <v>0.850256</v>
+        <v>0.838268</v>
       </c>
       <c r="F85" s="101" t="n">
         <v>0.8087257009</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="H85" s="101" t="n">
-        <v>0.803268</v>
+        <v>0.8113939999999999</v>
       </c>
       <c r="I85" s="101" t="n">
         <v>0.8207995184</v>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="N85" s="101" t="n">
-        <v>0.0226214238190286</v>
+        <v>0.0199302441454908</v>
       </c>
       <c r="O85" s="101" t="n">
         <v>0.0611152139</v>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0</v>
@@ -10291,10 +10291,10 @@
     <row r="132" ht="13.5" customHeight="1">
       <c r="B132" s="84" t="n"/>
       <c r="C132" s="95" t="n">
-        <v>0.1996959750892681</v>
+        <v>0.2113332251516544</v>
       </c>
       <c r="D132" s="95" t="n">
-        <v>0.319269</v>
+        <v>0.336799</v>
       </c>
       <c r="E132" s="85" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="I132" s="1" t="n">
-        <v>7407967.666666667</v>
+        <v>7910818.583333333</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>1369228.307039</v>
+        <v>1499932.800393</v>
       </c>
     </row>
     <row r="133">
@@ -10328,17 +10328,17 @@
         </is>
       </c>
       <c r="C133" s="112" t="n">
-        <v>0.1892211185637026</v>
+        <v>0</v>
       </c>
       <c r="D133" s="112" t="n">
-        <v>0.313798</v>
+        <v>0</v>
       </c>
       <c r="E133" s="21">
         <f>D133/C133</f>
         <v/>
       </c>
       <c r="F133" s="21" t="n">
-        <v>2.037636278655495</v>
+        <v>0</v>
       </c>
       <c r="G133" s="22">
         <f>E133-F133</f>
@@ -10349,10 +10349,10 @@
         <v/>
       </c>
       <c r="I133" s="103" t="n">
-        <v>7043976.25</v>
+        <v>4348799</v>
       </c>
       <c r="J133" s="103" t="n">
-        <v>1344905.21006</v>
+        <v>2267468.34835</v>
       </c>
     </row>
     <row r="134">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C1" s="12" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="D1" s="12" t="inlineStr">
         <is>
@@ -1916,28 +1916,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="100" t="n">
-        <v>26229219.03465001</v>
+        <v>30508558.42402</v>
       </c>
       <c r="E6" s="101">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="100" t="n">
-        <v>25198952.36185999</v>
+        <v>29485954.68686</v>
       </c>
       <c r="G6" s="101">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="100" t="n">
-        <v>28515941.75414003</v>
+        <v>33149266.88251022</v>
       </c>
       <c r="I6" s="101">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="100" t="n">
-        <v>27900000</v>
+        <v>32900000</v>
       </c>
       <c r="K6" s="101">
         <f>D6/J6</f>
@@ -1955,28 +1955,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="100" t="n">
-        <v>36650853.98930001</v>
+        <v>43127673.19754</v>
       </c>
       <c r="E7" s="101">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="100" t="n">
-        <v>42700003.63986</v>
+        <v>49748016.49318</v>
       </c>
       <c r="G7" s="101">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="100" t="n">
-        <v>52417550.64122663</v>
+        <v>60934455.2080678</v>
       </c>
       <c r="I7" s="101">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="100" t="n">
-        <v>53561034.7</v>
+        <v>62402640</v>
       </c>
       <c r="K7" s="101">
         <f>D7/J7</f>
@@ -1994,28 +1994,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="100" t="n">
-        <v>5001488.85697</v>
+        <v>5644151.23485</v>
       </c>
       <c r="E8" s="101">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="100" t="n">
-        <v>3061055.493069999</v>
+        <v>3502930.55547</v>
       </c>
       <c r="G8" s="101">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="100" t="n">
-        <v>3747464.916039146</v>
+        <v>4356360.231960072</v>
       </c>
       <c r="I8" s="101">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="100" t="n">
-        <v>3917018.15389968</v>
+        <v>4547018.15389968</v>
       </c>
       <c r="K8" s="101">
         <f>D8/J8</f>
@@ -2033,28 +2033,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="100" t="n">
-        <v>29396598.11794</v>
+        <v>34609754.73763</v>
       </c>
       <c r="E9" s="101">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="100" t="n">
-        <v>28718076.21583001</v>
+        <v>33890878.31298999</v>
       </c>
       <c r="G9" s="101">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="100" t="n">
-        <v>34945033.76081775</v>
+        <v>40622970.13871186</v>
       </c>
       <c r="I9" s="101">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="100" t="n">
-        <v>31909566</v>
+        <v>37685844</v>
       </c>
       <c r="K9" s="101">
         <f>D9/J9</f>
@@ -2072,28 +2072,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="100" t="n">
-        <v>24001794.60806</v>
+        <v>28161318.03415001</v>
       </c>
       <c r="E10" s="101">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="100" t="n">
-        <v>23336710.93771</v>
+        <v>26851775.95578999</v>
       </c>
       <c r="G10" s="101">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="100" t="n">
-        <v>26208775.32061331</v>
+        <v>30467227.6040339</v>
       </c>
       <c r="I10" s="101">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="100" t="n">
-        <v>27200000</v>
+        <v>31700000</v>
       </c>
       <c r="K10" s="101">
         <f>D10/J10</f>
@@ -2111,28 +2111,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="100" t="n">
-        <v>18107267.64684</v>
+        <v>21134327.21095</v>
       </c>
       <c r="E11" s="101">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="100" t="n">
-        <v>20723865.86578</v>
+        <v>24119991.46939</v>
       </c>
       <c r="G11" s="101">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="100" t="n">
-        <v>24775551.22192417</v>
+        <v>28801130.49387993</v>
       </c>
       <c r="I11" s="101">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="100" t="n">
-        <v>25300548.09</v>
+        <v>29345481.26</v>
       </c>
       <c r="K11" s="101">
         <f>D11/J11</f>
@@ -3979,40 +3979,40 @@
         </is>
       </c>
       <c r="C45" s="104" t="n">
-        <v>113.993424552</v>
+        <v>101.893415472</v>
       </c>
       <c r="D45" s="105" t="n">
-        <v>117.112</v>
+        <v>104.816</v>
       </c>
       <c r="E45" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.973371</v>
+        <v>0.972117</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.026629</v>
+        <v>0.027883</v>
       </c>
       <c r="H45" s="101" t="n">
-        <v>0.795024</v>
+        <v>0.793841</v>
       </c>
       <c r="I45" s="101" t="n">
-        <v>0.82358</v>
+        <v>0.816249</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>-2.8556</v>
+        <v>-2.2408</v>
       </c>
       <c r="K45" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L45" s="101" t="n">
-        <v>0.992406</v>
+        <v>0.984745</v>
       </c>
       <c r="M45" s="101" t="n">
-        <v>0.8542799999999999</v>
+        <v>0.846949</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>13.8126</v>
+        <v>13.77960000000002</v>
       </c>
       <c r="O45" s="15" t="n">
         <v>-2</v>
@@ -4035,31 +4035,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.531453</v>
+        <v>0.531129</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0.468547</v>
+        <v>0.468871</v>
       </c>
       <c r="H46" s="101" t="n">
-        <v>0.8861830000000001</v>
+        <v>0.875091</v>
       </c>
       <c r="I46" s="101" t="n">
-        <v>0.861343</v>
+        <v>0.858206</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>2.484</v>
+        <v>1.6885</v>
       </c>
       <c r="K46" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="101" t="n">
-        <v>0.949923</v>
+        <v>0.951449</v>
       </c>
       <c r="M46" s="101" t="n">
-        <v>0.8920429999999999</v>
+        <v>0.888906</v>
       </c>
       <c r="N46" s="15" t="n">
-        <v>5.788000000000011</v>
+        <v>6.254300000000015</v>
       </c>
       <c r="O46" s="15" t="n">
         <v>-2</v>
@@ -4073,40 +4073,40 @@
         </is>
       </c>
       <c r="C47" s="104" t="n">
-        <v>120</v>
+        <v>114.822931908</v>
       </c>
       <c r="D47" s="105" t="n">
-        <v>120</v>
+        <v>114.348</v>
       </c>
       <c r="E47" s="105" t="n">
         <v>120</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.919815</v>
+        <v>0.915971</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.08018500000000001</v>
+        <v>0.08402900000000001</v>
       </c>
       <c r="H47" s="101" t="n">
-        <v>0.755246</v>
+        <v>0.756567</v>
       </c>
       <c r="I47" s="101" t="n">
-        <v>0.788981</v>
+        <v>0.783741</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>-3.3735</v>
+        <v>-2.7174</v>
       </c>
       <c r="K47" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="101" t="n">
-        <v>0.77584</v>
+        <v>0.7614880000000001</v>
       </c>
       <c r="M47" s="101" t="n">
-        <v>0.8196809999999999</v>
+        <v>0.814441</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>-4.384099999999989</v>
+        <v>-5.295299999999997</v>
       </c>
       <c r="O47" s="15" t="n">
         <v>-2</v>
@@ -4120,40 +4120,40 @@
         </is>
       </c>
       <c r="C48" s="104" t="n">
-        <v>78.170427864</v>
+        <v>77.34217518</v>
       </c>
       <c r="D48" s="105" t="n">
-        <v>89.514</v>
+        <v>88.61</v>
       </c>
       <c r="E48" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.8732760000000001</v>
+        <v>0.872838</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.126724</v>
+        <v>0.127162</v>
       </c>
       <c r="H48" s="101" t="n">
-        <v>0.812524</v>
+        <v>0.812604</v>
       </c>
       <c r="I48" s="101" t="n">
-        <v>0.827281</v>
+        <v>0.826909</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>-1.4757</v>
+        <v>-1.4305</v>
       </c>
       <c r="K48" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="101" t="n">
-        <v>0.876089</v>
+        <v>0.875066</v>
       </c>
       <c r="M48" s="101" t="n">
-        <v>0.8579809999999999</v>
+        <v>0.857609</v>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1.810800000000015</v>
+        <v>1.745700000000014</v>
       </c>
       <c r="O48" s="15" t="n">
         <v>-2</v>
@@ -4176,31 +4176,31 @@
         <v>0</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.82184</v>
+        <v>0.820749</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.17816</v>
+        <v>0.179251</v>
       </c>
       <c r="H49" s="101" t="n">
-        <v>0.885202</v>
+        <v>0.884773</v>
       </c>
       <c r="I49" s="101" t="n">
-        <v>0.83172</v>
+        <v>0.830915</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>5.3482</v>
+        <v>5.3858</v>
       </c>
       <c r="K49" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="101" t="n">
-        <v>0.885636</v>
+        <v>0.886325</v>
       </c>
       <c r="M49" s="101" t="n">
-        <v>0.8624199999999999</v>
+        <v>0.8616149999999999</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>2.321600000000004</v>
+        <v>2.471000000000004</v>
       </c>
       <c r="O49" s="15" t="n">
         <v>-2</v>
@@ -4231,13 +4231,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="101" t="n">
-        <v>0.725952</v>
+        <v>0.719836</v>
       </c>
       <c r="I50" s="101" t="n">
-        <v>0.851125</v>
+        <v>0.847011</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>-12.5173</v>
+        <v>-12.7175</v>
       </c>
       <c r="K50" s="106" t="n">
         <v>-2</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="M50" s="101" t="n">
-        <v>0.8818249999999999</v>
+        <v>0.8777109999999999</v>
       </c>
       <c r="N50" s="15" t="inlineStr">
         <is>
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="C79" s="83" t="n">
-        <v>1438.333333333333</v>
+        <v>1429.357142857143</v>
       </c>
       <c r="D79" s="83" t="n">
-        <v>0.7069524913093859</v>
+        <v>0.7097096596871721</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>0.892247</v>
+        <v>0.8934</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>0.8146325152</v>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="H79" s="83" t="n">
-        <v>0.8853529999999999</v>
+        <v>0.885124</v>
       </c>
       <c r="I79" s="83" t="n">
         <v>0.8207995184</v>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0.7703349282296651</v>
+        <v>0.7719298245614035</v>
       </c>
       <c r="L79" s="13" t="n">
         <v>0.8082191781</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="N79" s="83" t="n">
-        <v>0.0641322366998486</v>
+        <v>0.0662968923763409</v>
       </c>
       <c r="O79" s="83" t="n">
         <v>0.0611152139</v>
@@ -7533,13 +7533,13 @@
         </is>
       </c>
       <c r="C80" s="19" t="n">
-        <v>112.5</v>
+        <v>113.2142857142857</v>
       </c>
       <c r="D80" s="101" t="n">
-        <v>0.2422222222222222</v>
+        <v>0.2460567823343849</v>
       </c>
       <c r="E80" s="101" t="n">
-        <v>0.725952</v>
+        <v>0.719836</v>
       </c>
       <c r="F80" s="101" t="n">
         <v>0.7556221149</v>
@@ -7559,7 +7559,7 @@
         <v>0.1598504816</v>
       </c>
       <c r="K80" s="101" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L80" s="101" t="n">
         <v>0.8082191781</v>
@@ -7568,7 +7568,7 @@
         <v>-0.1240086517842105</v>
       </c>
       <c r="N80" s="101" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.1555285540704739</v>
       </c>
       <c r="O80" s="101" t="n">
         <v>0.0611152139</v>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="C81" s="19" t="n">
-        <v>343.5833333333333</v>
+        <v>336</v>
       </c>
       <c r="D81" s="101" t="n">
-        <v>0.7184089255396556</v>
+        <v>0.71875</v>
       </c>
       <c r="E81" s="101" t="n">
-        <v>0.883168</v>
+        <v>0.8849050000000001</v>
       </c>
       <c r="F81" s="101" t="n">
         <v>0.8066</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="H81" s="101" t="n">
-        <v>0.8847429999999999</v>
+        <v>0.884486</v>
       </c>
       <c r="I81" s="101" t="n">
         <v>0.8207995184</v>
@@ -7621,7 +7621,7 @@
         <v>-0.8082191781</v>
       </c>
       <c r="N81" s="101" t="n">
-        <v>0.055196513113399</v>
+        <v>0.0559707635070622</v>
       </c>
       <c r="O81" s="101" t="n">
         <v>0.0611152139</v>
@@ -7637,13 +7637,13 @@
         </is>
       </c>
       <c r="C82" s="19" t="n">
-        <v>884.0833333333334</v>
+        <v>881.8571428571429</v>
       </c>
       <c r="D82" s="101" t="n">
-        <v>0.7984729946272033</v>
+        <v>0.8026891300826179</v>
       </c>
       <c r="E82" s="101" t="n">
-        <v>0.909911</v>
+        <v>0.909886</v>
       </c>
       <c r="F82" s="101" t="n">
         <v>0.8078</v>
@@ -7652,7 +7652,7 @@
         <v>0.15917</v>
       </c>
       <c r="H82" s="101" t="n">
-        <v>0.887755</v>
+        <v>0.889021</v>
       </c>
       <c r="I82" s="101" t="n">
         <v>0.8207995184</v>
@@ -7661,7 +7661,7 @@
         <v>0.1714954816000001</v>
       </c>
       <c r="K82" s="101" t="n">
-        <v>0.7459459459459459</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="L82" s="101" t="n">
         <v>0.8082191781</v>
@@ -7670,7 +7670,7 @@
         <v>0.1917808219</v>
       </c>
       <c r="N82" s="101" t="n">
-        <v>0.0700038573046151</v>
+        <v>0.07326775021385799</v>
       </c>
       <c r="O82" s="101" t="n">
         <v>0.0611152139</v>
@@ -7742,7 +7742,7 @@
         <v>2</v>
       </c>
       <c r="D84" s="101" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E84" s="101" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="N84" s="101" t="n">
-        <v>0.25</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="O84" s="101" t="n">
         <v>0.0611152139</v>
@@ -7800,13 +7800,13 @@
         </is>
       </c>
       <c r="C85" s="19" t="n">
-        <v>95.33333333333333</v>
+        <v>95.57142857142857</v>
       </c>
       <c r="D85" s="101" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3684603886397608</v>
       </c>
       <c r="E85" s="101" t="n">
-        <v>0.838268</v>
+        <v>0.834846</v>
       </c>
       <c r="F85" s="101" t="n">
         <v>0.8087257009</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="H85" s="101" t="n">
-        <v>0.8113939999999999</v>
+        <v>0.783925</v>
       </c>
       <c r="I85" s="101" t="n">
         <v>0.8207995184</v>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="N85" s="101" t="n">
-        <v>0.0199302441454908</v>
+        <v>0.0200597524541187</v>
       </c>
       <c r="O85" s="101" t="n">
         <v>0.0611152139</v>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0</v>
@@ -10291,10 +10291,10 @@
     <row r="132" ht="13.5" customHeight="1">
       <c r="B132" s="84" t="n"/>
       <c r="C132" s="95" t="n">
-        <v>0.2113332251516544</v>
+        <v>0.2120896400537903</v>
       </c>
       <c r="D132" s="95" t="n">
-        <v>0.336799</v>
+        <v>0.335456</v>
       </c>
       <c r="E132" s="85" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="I132" s="1" t="n">
-        <v>7910818.583333333</v>
+        <v>7910742.785714285</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>1499932.800393</v>
+        <v>1491319.224516</v>
       </c>
     </row>
     <row r="133">
@@ -10349,10 +10349,10 @@
         <v/>
       </c>
       <c r="I133" s="103" t="n">
-        <v>4348799</v>
+        <v>4985627</v>
       </c>
       <c r="J133" s="103" t="n">
-        <v>2267468.34835</v>
+        <v>2620680.62821</v>
       </c>
     </row>
     <row r="134">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9347,25 +9347,22 @@
         <f>SUM(C116:C118)</f>
         <v/>
       </c>
-      <c r="D115" s="100">
-        <f>SUM(D116:D118)</f>
-        <v/>
+      <c r="D115" s="100" t="n">
+        <v>249044.42849</v>
       </c>
       <c r="E115" s="101">
         <f>D115/C115</f>
         <v/>
       </c>
-      <c r="F115" s="100">
-        <f>SUM(F116:F118)</f>
-        <v/>
+      <c r="F115" s="100" t="n">
+        <v>672015.4754599999</v>
       </c>
       <c r="G115" s="101">
         <f>D115/F115-1</f>
         <v/>
       </c>
-      <c r="H115" s="100">
-        <f>SUM(H116:H118)</f>
-        <v/>
+      <c r="H115" s="100" t="n">
+        <v>2407233.682542903</v>
       </c>
       <c r="I115" s="101">
         <f>D115/H115</f>
@@ -9383,22 +9380,21 @@
         <v>1705697.009344685</v>
       </c>
       <c r="D116" s="100" t="n">
-        <v>179111.31</v>
+        <v>75973.64268</v>
       </c>
       <c r="E116" s="101">
         <f>D116/C116</f>
         <v/>
       </c>
       <c r="F116" s="100" t="n">
-        <v>78837.21000000001</v>
+        <v>316164.28121</v>
       </c>
       <c r="G116" s="101">
         <f>D116/F116-1</f>
         <v/>
       </c>
-      <c r="H116" s="100">
-        <f>C116*H12/C12</f>
-        <v/>
+      <c r="H116" s="100" t="n">
+        <v>770314.7784137286</v>
       </c>
       <c r="I116" s="101">
         <f>D116/H116</f>
@@ -9415,22 +9411,21 @@
         <v>2665151.577101071</v>
       </c>
       <c r="D117" s="100" t="n">
-        <v>347193.34</v>
+        <v>173070.78581</v>
       </c>
       <c r="E117" s="101">
         <f>D117/C117</f>
         <v/>
       </c>
       <c r="F117" s="100" t="n">
-        <v>615447.34</v>
+        <v>352376.49425</v>
       </c>
       <c r="G117" s="101">
         <f>D117/F117-1</f>
         <v/>
       </c>
-      <c r="H117" s="100">
-        <f>C117*H12/C12</f>
-        <v/>
+      <c r="H117" s="100" t="n">
+        <v>1203616.841271451</v>
       </c>
       <c r="I117" s="101">
         <f>D117/H117</f>
@@ -9446,23 +9441,20 @@
       <c r="C118" s="100" t="n">
         <v>959454.5677563855</v>
       </c>
-      <c r="D118" s="100" t="n">
-        <v>742</v>
-      </c>
+      <c r="D118" s="100" t="n"/>
       <c r="E118" s="101">
         <f>D118/C118</f>
         <v/>
       </c>
       <c r="F118" s="100" t="n">
-        <v>30429.86</v>
+        <v>3474.7</v>
       </c>
       <c r="G118" s="101">
         <f>D118/F118-1</f>
         <v/>
       </c>
-      <c r="H118" s="100">
-        <f>C118*H12/C12</f>
-        <v/>
+      <c r="H118" s="100" t="n">
+        <v>433302.0628577225</v>
       </c>
       <c r="I118" s="101">
         <f>D118/H118</f>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -387,7 +387,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -756,6 +756,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1803,6 +1809,7 @@
     <col width="8.6640625" customWidth="1" style="1" min="1" max="1"/>
     <col width="8.4140625" customWidth="1" style="1" min="2" max="2"/>
     <col width="8.6640625" customWidth="1" style="1" min="3" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9.6640625" customWidth="1" style="1" min="5" max="5"/>
     <col width="9.25" customWidth="1" style="1" min="6" max="6"/>
     <col width="11.08203125" customWidth="1" style="1" min="7" max="7"/>
@@ -3730,21 +3737,21 @@
           <t>7月MTD</t>
         </is>
       </c>
-      <c r="C36" s="100" t="n">
-        <v>22775804.083216</v>
-      </c>
-      <c r="D36" s="100" t="n">
-        <v>15291376.497635</v>
+      <c r="C36" s="128" t="n">
+        <v>139555019.522971</v>
+      </c>
+      <c r="D36" s="128" t="n">
+        <v>94626317.035368</v>
       </c>
       <c r="E36" s="100">
         <f>D36*F36</f>
         <v/>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>0.1967206649980933</v>
+      <c r="F36" s="129" t="n">
+        <v>0.1996835830893531</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2088749940488895</v>
+        <v>0.208874994</v>
       </c>
       <c r="H36" s="3">
         <f>F36-G36</f>
@@ -3760,7 +3767,7 @@
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>截止3号0点</t>
+          <t>截止13号0点</t>
         </is>
       </c>
     </row>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -3698,17 +3698,17 @@
         </is>
       </c>
       <c r="C35" s="100" t="n">
-        <v>401017967.9744362</v>
+        <v>400099823.8179032</v>
       </c>
       <c r="D35" s="100" t="n">
-        <v>266882255.703103</v>
+        <v>264735399.3403789</v>
       </c>
       <c r="E35" s="100">
         <f>D35*F35</f>
         <v/>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.202198147827591</v>
+        <v>0.2040093440076088</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.2091475907</v>
@@ -3725,33 +3725,32 @@
         <f>D35*H35</f>
         <v/>
       </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>待15号更新最终</t>
-        </is>
-      </c>
+      <c r="K35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>7月MTD</t>
-        </is>
-      </c>
-      <c r="C36" s="128" t="n">
-        <v>139555019.522971</v>
-      </c>
-      <c r="D36" s="128" t="n">
-        <v>94626317.035368</v>
+          <t>6月YTD</t>
+        </is>
+      </c>
+      <c r="C36" s="100">
+        <f>C34+C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="100">
+        <f>D34+D35</f>
+        <v/>
       </c>
       <c r="E36" s="100">
-        <f>D36*F36</f>
-        <v/>
-      </c>
-      <c r="F36" s="129" t="n">
-        <v>0.1996835830893531</v>
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="3">
+        <f>E36/D36</f>
+        <v/>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.208874994</v>
+        <v>0.1935933117580375</v>
       </c>
       <c r="H36" s="3">
         <f>F36-G36</f>
@@ -3765,37 +3764,29 @@
         <f>D36*H36</f>
         <v/>
       </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>截止13号0点</t>
-        </is>
-      </c>
+      <c r="K36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>YTD</t>
-        </is>
-      </c>
-      <c r="C37" s="100">
-        <f>C34+C35+C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="100">
-        <f>D34+D35+D36</f>
-        <v/>
+          <t>7月MTD</t>
+        </is>
+      </c>
+      <c r="C37" s="128" t="n">
+        <v>139555019.522971</v>
+      </c>
+      <c r="D37" s="128" t="n">
+        <v>94626317.035368</v>
       </c>
       <c r="E37" s="100">
-        <f>E34+E35+E36</f>
-        <v/>
-      </c>
-      <c r="F37" s="3">
-        <f>E37/D37</f>
-        <v/>
-      </c>
-      <c r="G37" s="3">
-        <f>F37-(J37/D37)</f>
-        <v/>
+        <f>D37*F37</f>
+        <v/>
+      </c>
+      <c r="F37" s="129" t="n">
+        <v>0.1996835830893531</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.208874994</v>
       </c>
       <c r="H37" s="3">
         <f>F37-G37</f>
@@ -3806,34 +3797,40 @@
         <v/>
       </c>
       <c r="J37" s="100">
-        <f>SUM(J34:J36)</f>
-        <v/>
+        <f>D37*H37</f>
+        <v/>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>截止13号0点</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>全年目标</t>
+          <t>YTD</t>
         </is>
       </c>
       <c r="C38" s="100">
-        <f>C37</f>
+        <f>C36+C37</f>
         <v/>
       </c>
       <c r="D38" s="100">
-        <f>D37</f>
+        <f>D36+D37</f>
         <v/>
       </c>
       <c r="E38" s="100">
-        <f>E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="11">
-        <f>F37</f>
-        <v/>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0.1914701443277041</v>
+        <f>E36+E37</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>E38/D38</f>
+        <v/>
+      </c>
+      <c r="G38" s="3">
+        <f>F38-(J38/D38)</f>
+        <v/>
       </c>
       <c r="H38" s="3">
         <f>F38-G38</f>
@@ -3844,7 +3841,7 @@
         <v/>
       </c>
       <c r="J38" s="100">
-        <f>D38*H38</f>
+        <f>SUM(J34:J37)</f>
         <v/>
       </c>
     </row>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C1" s="12" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="D1" s="12" t="inlineStr">
         <is>
@@ -1923,28 +1923,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="100" t="n">
-        <v>30508558.42402</v>
+        <v>32389627.70686</v>
       </c>
       <c r="E6" s="101">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="100" t="n">
-        <v>29485954.68686</v>
+        <v>31643223.77757</v>
       </c>
       <c r="G6" s="101">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="100" t="n">
-        <v>33149266.88251022</v>
+        <v>35522514.17281207</v>
       </c>
       <c r="I6" s="101">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="100" t="n">
-        <v>32900000</v>
+        <v>35000000</v>
       </c>
       <c r="K6" s="101">
         <f>D6/J6</f>
@@ -1962,28 +1962,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="100" t="n">
-        <v>43127673.19754</v>
+        <v>46036869.25590001</v>
       </c>
       <c r="E7" s="101">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="100" t="n">
-        <v>49748016.49318</v>
+        <v>53288833.82045999</v>
       </c>
       <c r="G7" s="101">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="100" t="n">
-        <v>60934455.2080678</v>
+        <v>65296920.63516492</v>
       </c>
       <c r="I7" s="101">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="100" t="n">
-        <v>62402640</v>
+        <v>66844327.6</v>
       </c>
       <c r="K7" s="101">
         <f>D7/J7</f>
@@ -2001,28 +2001,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="100" t="n">
-        <v>5644151.23485</v>
+        <v>5911715.114849999</v>
       </c>
       <c r="E8" s="101">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="100" t="n">
-        <v>3502930.55547</v>
+        <v>3735617.23936</v>
       </c>
       <c r="G8" s="101">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="100" t="n">
-        <v>4356360.231960072</v>
+        <v>4668244.055898658</v>
       </c>
       <c r="I8" s="101">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="100" t="n">
-        <v>4547018.15389968</v>
+        <v>4807018.15389968</v>
       </c>
       <c r="K8" s="101">
         <f>D8/J8</f>
@@ -2040,28 +2040,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="100" t="n">
-        <v>34609754.73763</v>
+        <v>38550501.94708</v>
       </c>
       <c r="E9" s="101">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="100" t="n">
-        <v>33890878.31298999</v>
+        <v>36103787.69422</v>
       </c>
       <c r="G9" s="101">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="100" t="n">
-        <v>40622970.13871186</v>
+        <v>43531280.42344328</v>
       </c>
       <c r="I9" s="101">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="100" t="n">
-        <v>37685844</v>
+        <v>42022350</v>
       </c>
       <c r="K9" s="101">
         <f>D9/J9</f>
@@ -2079,28 +2079,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="100" t="n">
-        <v>28161318.03415001</v>
+        <v>29962467.94621</v>
       </c>
       <c r="E10" s="101">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="100" t="n">
-        <v>26851775.95578999</v>
+        <v>29040917.19023</v>
       </c>
       <c r="G10" s="101">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="100" t="n">
-        <v>30467227.6040339</v>
+        <v>32648460.31758246</v>
       </c>
       <c r="I10" s="101">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="100" t="n">
-        <v>31700000</v>
+        <v>34200000</v>
       </c>
       <c r="K10" s="101">
         <f>D10/J10</f>
@@ -2118,28 +2118,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="100" t="n">
-        <v>21134327.21095</v>
+        <v>22614057.90135</v>
       </c>
       <c r="E11" s="101">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="100" t="n">
-        <v>24119991.46939</v>
+        <v>26008759.14053</v>
       </c>
       <c r="G11" s="101">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="100" t="n">
-        <v>28801130.49387993</v>
+        <v>30863082.72783095</v>
       </c>
       <c r="I11" s="101">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="100" t="n">
-        <v>29345481.26</v>
+        <v>31258269.39</v>
       </c>
       <c r="K11" s="101">
         <f>D11/J11</f>
@@ -3983,40 +3983,40 @@
         </is>
       </c>
       <c r="C45" s="104" t="n">
-        <v>101.893415472</v>
+        <v>97.93021553000001</v>
       </c>
       <c r="D45" s="105" t="n">
-        <v>104.816</v>
+        <v>100.814</v>
       </c>
       <c r="E45" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.972117</v>
+        <v>0.971395</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.027883</v>
+        <v>0.028605</v>
       </c>
       <c r="H45" s="101" t="n">
-        <v>0.793841</v>
+        <v>0.793439</v>
       </c>
       <c r="I45" s="101" t="n">
-        <v>0.816249</v>
+        <v>0.813846</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>-2.2408</v>
+        <v>-2.0407</v>
       </c>
       <c r="K45" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L45" s="101" t="n">
-        <v>0.984745</v>
+        <v>0.985509</v>
       </c>
       <c r="M45" s="101" t="n">
-        <v>0.846949</v>
+        <v>0.844546</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>13.77960000000002</v>
+        <v>14.0963</v>
       </c>
       <c r="O45" s="15" t="n">
         <v>-2</v>
@@ -4039,31 +4039,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.531129</v>
+        <v>0.545478</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>0.468871</v>
+        <v>0.454522</v>
       </c>
       <c r="H46" s="101" t="n">
-        <v>0.875091</v>
+        <v>0.871382</v>
       </c>
       <c r="I46" s="101" t="n">
-        <v>0.858206</v>
+        <v>0.855704</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>1.6885</v>
+        <v>1.5678</v>
       </c>
       <c r="K46" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="101" t="n">
-        <v>0.951449</v>
+        <v>0.949881</v>
       </c>
       <c r="M46" s="101" t="n">
-        <v>0.888906</v>
+        <v>0.886404</v>
       </c>
       <c r="N46" s="15" t="n">
-        <v>6.254300000000015</v>
+        <v>6.347700000000003</v>
       </c>
       <c r="O46" s="15" t="n">
         <v>-2</v>
@@ -4077,40 +4077,40 @@
         </is>
       </c>
       <c r="C47" s="104" t="n">
-        <v>114.822931908</v>
+        <v>109.59882038</v>
       </c>
       <c r="D47" s="105" t="n">
-        <v>114.348</v>
+        <v>108.652</v>
       </c>
       <c r="E47" s="105" t="n">
         <v>120</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.915971</v>
+        <v>0.916565</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.08402900000000001</v>
+        <v>0.083435</v>
       </c>
       <c r="H47" s="101" t="n">
-        <v>0.756567</v>
+        <v>0.756123</v>
       </c>
       <c r="I47" s="101" t="n">
-        <v>0.783741</v>
+        <v>0.7804489999999999</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>-2.7174</v>
+        <v>-2.4326</v>
       </c>
       <c r="K47" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="101" t="n">
-        <v>0.7614880000000001</v>
+        <v>0.75467</v>
       </c>
       <c r="M47" s="101" t="n">
-        <v>0.814441</v>
+        <v>0.8111489999999999</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>-5.295299999999997</v>
+        <v>-5.647899999999993</v>
       </c>
       <c r="O47" s="15" t="n">
         <v>-2</v>
@@ -4124,40 +4124,40 @@
         </is>
       </c>
       <c r="C48" s="104" t="n">
-        <v>77.34217518</v>
+        <v>78.824133768</v>
       </c>
       <c r="D48" s="105" t="n">
-        <v>88.61</v>
+        <v>90.294</v>
       </c>
       <c r="E48" s="105" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.872838</v>
+        <v>0.872972</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.127162</v>
+        <v>0.127028</v>
       </c>
       <c r="H48" s="101" t="n">
-        <v>0.812604</v>
+        <v>0.811846</v>
       </c>
       <c r="I48" s="101" t="n">
-        <v>0.826909</v>
+        <v>0.826993</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>-1.4305</v>
+        <v>-1.5147</v>
       </c>
       <c r="K48" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="101" t="n">
-        <v>0.875066</v>
+        <v>0.873203</v>
       </c>
       <c r="M48" s="101" t="n">
-        <v>0.857609</v>
+        <v>0.8576929999999998</v>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1.745700000000014</v>
+        <v>1.551000000000016</v>
       </c>
       <c r="O48" s="15" t="n">
         <v>-2</v>
@@ -4180,31 +4180,31 @@
         <v>0</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.820749</v>
+        <v>0.820505</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.179251</v>
+        <v>0.179495</v>
       </c>
       <c r="H49" s="101" t="n">
-        <v>0.884773</v>
+        <v>0.884324</v>
       </c>
       <c r="I49" s="101" t="n">
-        <v>0.830915</v>
+        <v>0.831376</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>5.3858</v>
+        <v>5.2948</v>
       </c>
       <c r="K49" s="106" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="101" t="n">
-        <v>0.886325</v>
+        <v>0.887052</v>
       </c>
       <c r="M49" s="101" t="n">
-        <v>0.8616149999999999</v>
+        <v>0.862076</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>2.471000000000004</v>
+        <v>2.497600000000006</v>
       </c>
       <c r="O49" s="15" t="n">
         <v>-2</v>
@@ -4235,13 +4235,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="101" t="n">
-        <v>0.719836</v>
+        <v>0.726978</v>
       </c>
       <c r="I50" s="101" t="n">
-        <v>0.847011</v>
+        <v>0.847102</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>-12.7175</v>
+        <v>-12.0124</v>
       </c>
       <c r="K50" s="106" t="n">
         <v>-2</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="M50" s="101" t="n">
-        <v>0.8777109999999999</v>
+        <v>0.877802</v>
       </c>
       <c r="N50" s="15" t="inlineStr">
         <is>
@@ -6709,15 +6709,11 @@
     </row>
     <row r="67" ht="27" customFormat="1" customHeight="1" s="10">
       <c r="B67" s="84" t="n"/>
-      <c r="C67" s="83" t="inlineStr">
-        <is>
-          <t>去年内网价指</t>
-        </is>
-      </c>
-      <c r="D67" s="83" t="inlineStr">
-        <is>
-          <t>今年内网价指</t>
-        </is>
+      <c r="C67" s="83" t="n">
+        <v>0.9442551200979122</v>
+      </c>
+      <c r="D67" s="83" t="n">
+        <v>0.9351252719748095</v>
       </c>
       <c r="E67" s="83" t="inlineStr">
         <is>
@@ -6837,10 +6833,10 @@
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.9571694091959044</v>
+        <v>0.9385070529208377</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>0.9534994973348581</v>
+        <v>0.8904571310876348</v>
       </c>
       <c r="E68" s="11">
         <f>D68-C68</f>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0.9589185714822225</v>
+        <v>0.933685712972067</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>0.9079251194593112</v>
+        <v>0.8888831732323637</v>
       </c>
       <c r="E69" s="11">
         <f>D69-C69</f>
@@ -7015,10 +7011,10 @@
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>0.9681390499279691</v>
+        <v>0.9779898468577517</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>0.8981930752223342</v>
+        <v>0.8722023115804697</v>
       </c>
       <c r="E70" s="11">
         <f>D70-C70</f>
@@ -7104,10 +7100,10 @@
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>0.9569645315615172</v>
+        <v>0.962906447794792</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>0.8682322819409692</v>
+        <v>0.8449899596660958</v>
       </c>
       <c r="E71" s="11">
         <f>D71-C71</f>
@@ -7193,10 +7189,10 @@
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>0.987176939331088</v>
+        <v>0.9475576301941477</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>0.843760920920546</v>
+        <v>0.8800287196118829</v>
       </c>
       <c r="E72" s="11">
         <f>D72-C72</f>
@@ -7282,10 +7278,10 @@
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0.952955994800067</v>
+        <v>0.9430572607356902</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0.8952566212638129</v>
+        <v>0.8852976812028019</v>
       </c>
       <c r="E73" s="11">
         <f>D73-C73</f>
@@ -7480,13 +7476,13 @@
         </is>
       </c>
       <c r="C79" s="83" t="n">
-        <v>1429.357142857143</v>
+        <v>1426.133333333333</v>
       </c>
       <c r="D79" s="83" t="n">
-        <v>0.7097096596871721</v>
+        <v>0.7102655198204936</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>0.8934</v>
+        <v>0.894085</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>0.8146325152</v>
@@ -7497,7 +7493,7 @@
         </is>
       </c>
       <c r="H79" s="83" t="n">
-        <v>0.885124</v>
+        <v>0.885304</v>
       </c>
       <c r="I79" s="83" t="n">
         <v>0.8207995184</v>
@@ -7508,7 +7504,7 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.7725321888412017</v>
       </c>
       <c r="L79" s="13" t="n">
         <v>0.8082191781</v>
@@ -7519,7 +7515,7 @@
         </is>
       </c>
       <c r="N79" s="83" t="n">
-        <v>0.0662968923763409</v>
+        <v>0.0674717790657853</v>
       </c>
       <c r="O79" s="83" t="n">
         <v>0.0611152139</v>
@@ -7537,13 +7533,13 @@
         </is>
       </c>
       <c r="C80" s="19" t="n">
-        <v>113.2142857142857</v>
+        <v>113.6</v>
       </c>
       <c r="D80" s="101" t="n">
-        <v>0.2460567823343849</v>
+        <v>0.2488262910798122</v>
       </c>
       <c r="E80" s="101" t="n">
-        <v>0.719836</v>
+        <v>0.726978</v>
       </c>
       <c r="F80" s="101" t="n">
         <v>0.7556221149</v>
@@ -7572,7 +7568,7 @@
         <v>-0.1240086517842105</v>
       </c>
       <c r="N80" s="101" t="n">
-        <v>0.1555285540704739</v>
+        <v>0.1528878822197055</v>
       </c>
       <c r="O80" s="101" t="n">
         <v>0.0611152139</v>
@@ -7588,13 +7584,13 @@
         </is>
       </c>
       <c r="C81" s="19" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D81" s="101" t="n">
-        <v>0.71875</v>
+        <v>0.7187187187187187</v>
       </c>
       <c r="E81" s="101" t="n">
-        <v>0.8849050000000001</v>
+        <v>0.885275</v>
       </c>
       <c r="F81" s="101" t="n">
         <v>0.8066</v>
@@ -7605,7 +7601,7 @@
         </is>
       </c>
       <c r="H81" s="101" t="n">
-        <v>0.884486</v>
+        <v>0.884537</v>
       </c>
       <c r="I81" s="101" t="n">
         <v>0.8207995184</v>
@@ -7625,7 +7621,7 @@
         <v>-0.8082191781</v>
       </c>
       <c r="N81" s="101" t="n">
-        <v>0.0559707635070622</v>
+        <v>0.056609623015873</v>
       </c>
       <c r="O81" s="101" t="n">
         <v>0.0611152139</v>
@@ -7641,13 +7637,13 @@
         </is>
       </c>
       <c r="C82" s="19" t="n">
-        <v>881.8571428571429</v>
+        <v>881.2</v>
       </c>
       <c r="D82" s="101" t="n">
-        <v>0.8026891300826179</v>
+        <v>0.8033741867150855</v>
       </c>
       <c r="E82" s="101" t="n">
-        <v>0.909886</v>
+        <v>0.911267</v>
       </c>
       <c r="F82" s="101" t="n">
         <v>0.8078</v>
@@ -7656,7 +7652,7 @@
         <v>0.15917</v>
       </c>
       <c r="H82" s="101" t="n">
-        <v>0.889021</v>
+        <v>0.890388</v>
       </c>
       <c r="I82" s="101" t="n">
         <v>0.8207995184</v>
@@ -7665,7 +7661,7 @@
         <v>0.1714954816000001</v>
       </c>
       <c r="K82" s="101" t="n">
-        <v>0.7384615384615385</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="L82" s="101" t="n">
         <v>0.8082191781</v>
@@ -7674,7 +7670,7 @@
         <v>0.1917808219</v>
       </c>
       <c r="N82" s="101" t="n">
-        <v>0.07326775021385799</v>
+        <v>0.0750439437519974</v>
       </c>
       <c r="O82" s="101" t="n">
         <v>0.0611152139</v>
@@ -7746,7 +7742,7 @@
         <v>2</v>
       </c>
       <c r="D84" s="101" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E84" s="101" t="inlineStr">
         <is>
@@ -7788,7 +7784,7 @@
         </is>
       </c>
       <c r="N84" s="101" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="O84" s="101" t="n">
         <v>0.0611152139</v>
@@ -7804,13 +7800,13 @@
         </is>
       </c>
       <c r="C85" s="19" t="n">
-        <v>95.57142857142857</v>
+        <v>95.66666666666667</v>
       </c>
       <c r="D85" s="101" t="n">
-        <v>0.3684603886397608</v>
+        <v>0.3700348432055749</v>
       </c>
       <c r="E85" s="101" t="n">
-        <v>0.834846</v>
+        <v>0.832282</v>
       </c>
       <c r="F85" s="101" t="n">
         <v>0.8087257009</v>
@@ -7821,7 +7817,7 @@
         </is>
       </c>
       <c r="H85" s="101" t="n">
-        <v>0.783925</v>
+        <v>0.780199</v>
       </c>
       <c r="I85" s="101" t="n">
         <v>0.8207995184</v>
@@ -7831,10 +7827,8 @@
           <t>(NULL)</t>
         </is>
       </c>
-      <c r="K85" s="101" t="inlineStr">
-        <is>
-          <t>(NULL)</t>
-        </is>
+      <c r="K85" s="101" t="n">
+        <v>1</v>
       </c>
       <c r="L85" s="101" t="n">
         <v>0.8082191781</v>
@@ -7845,7 +7839,7 @@
         </is>
       </c>
       <c r="N85" s="101" t="n">
-        <v>0.0200597524541187</v>
+        <v>0.0195141377937077</v>
       </c>
       <c r="O85" s="101" t="n">
         <v>0.0611152139</v>
@@ -7957,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="5" t="n">
         <v>0</v>
@@ -7981,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0</v>
@@ -9352,21 +9346,21 @@
         <v/>
       </c>
       <c r="D115" s="100" t="n">
-        <v>249044.42849</v>
+        <v>84365723.00999999</v>
       </c>
       <c r="E115" s="101">
         <f>D115/C115</f>
         <v/>
       </c>
       <c r="F115" s="100" t="n">
-        <v>672015.4754599999</v>
+        <v>0</v>
       </c>
       <c r="G115" s="101">
         <f>D115/F115-1</f>
         <v/>
       </c>
       <c r="H115" s="100" t="n">
-        <v>2407233.682542903</v>
+        <v>2579178.945581681</v>
       </c>
       <c r="I115" s="101">
         <f>D115/H115</f>
@@ -9384,21 +9378,19 @@
         <v>1705697.009344685</v>
       </c>
       <c r="D116" s="100" t="n">
-        <v>75973.64268</v>
+        <v>6268788.85</v>
       </c>
       <c r="E116" s="101">
         <f>D116/C116</f>
         <v/>
       </c>
-      <c r="F116" s="100" t="n">
-        <v>316164.28121</v>
-      </c>
+      <c r="F116" s="100" t="n"/>
       <c r="G116" s="101">
         <f>D116/F116-1</f>
         <v/>
       </c>
       <c r="H116" s="100" t="n">
-        <v>770314.7784137286</v>
+        <v>825337.2625861379</v>
       </c>
       <c r="I116" s="101">
         <f>D116/H116</f>
@@ -9415,21 +9407,19 @@
         <v>2665151.577101071</v>
       </c>
       <c r="D117" s="100" t="n">
-        <v>173070.78581</v>
+        <v>32810952.58</v>
       </c>
       <c r="E117" s="101">
         <f>D117/C117</f>
         <v/>
       </c>
-      <c r="F117" s="100" t="n">
-        <v>352376.49425</v>
-      </c>
+      <c r="F117" s="100" t="n"/>
       <c r="G117" s="101">
         <f>D117/F117-1</f>
         <v/>
       </c>
       <c r="H117" s="100" t="n">
-        <v>1203616.841271451</v>
+        <v>1289589.472790841</v>
       </c>
       <c r="I117" s="101">
         <f>D117/H117</f>
@@ -9445,20 +9435,20 @@
       <c r="C118" s="100" t="n">
         <v>959454.5677563855</v>
       </c>
-      <c r="D118" s="100" t="n"/>
+      <c r="D118" s="100" t="n">
+        <v>45285981.58</v>
+      </c>
       <c r="E118" s="101">
         <f>D118/C118</f>
         <v/>
       </c>
-      <c r="F118" s="100" t="n">
-        <v>3474.7</v>
-      </c>
+      <c r="F118" s="100" t="n"/>
       <c r="G118" s="101">
         <f>D118/F118-1</f>
         <v/>
       </c>
       <c r="H118" s="100" t="n">
-        <v>433302.0628577225</v>
+        <v>464252.2102047027</v>
       </c>
       <c r="I118" s="101">
         <f>D118/H118</f>
@@ -10287,10 +10277,10 @@
     <row r="132" ht="13.5" customHeight="1">
       <c r="B132" s="84" t="n"/>
       <c r="C132" s="95" t="n">
-        <v>0.2120896400537903</v>
+        <v>0.2109305926466908</v>
       </c>
       <c r="D132" s="95" t="n">
-        <v>0.335456</v>
+        <v>0.333069</v>
       </c>
       <c r="E132" s="85" t="inlineStr">
         <is>
@@ -10311,10 +10301,10 @@
         </is>
       </c>
       <c r="I132" s="1" t="n">
-        <v>7910742.785714285</v>
+        <v>7848911.466666667</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>1491319.224516</v>
+        <v>1469871.58898</v>
       </c>
     </row>
     <row r="133">
@@ -10345,10 +10335,10 @@
         <v/>
       </c>
       <c r="I133" s="103" t="n">
-        <v>4985627</v>
+        <v>5270625</v>
       </c>
       <c r="J133" s="103" t="n">
-        <v>2620680.62821</v>
+        <v>2725288.33066</v>
       </c>
     </row>
     <row r="134">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9346,14 +9346,14 @@
         <v/>
       </c>
       <c r="D115" s="100" t="n">
-        <v>84365723.00999999</v>
+        <v>570428.7899999999</v>
       </c>
       <c r="E115" s="101">
         <f>D115/C115</f>
         <v/>
       </c>
       <c r="F115" s="100" t="n">
-        <v>0</v>
+        <v>696534.1799999999</v>
       </c>
       <c r="G115" s="101">
         <f>D115/F115-1</f>
@@ -9378,13 +9378,15 @@
         <v>1705697.009344685</v>
       </c>
       <c r="D116" s="100" t="n">
-        <v>6268788.85</v>
+        <v>246072.77</v>
       </c>
       <c r="E116" s="101">
         <f>D116/C116</f>
         <v/>
       </c>
-      <c r="F116" s="100" t="n"/>
+      <c r="F116" s="100" t="n">
+        <v>148274.21</v>
+      </c>
       <c r="G116" s="101">
         <f>D116/F116-1</f>
         <v/>
@@ -9407,13 +9409,15 @@
         <v>2665151.577101071</v>
       </c>
       <c r="D117" s="100" t="n">
-        <v>32810952.58</v>
+        <v>317214.3</v>
       </c>
       <c r="E117" s="101">
         <f>D117/C117</f>
         <v/>
       </c>
-      <c r="F117" s="100" t="n"/>
+      <c r="F117" s="100" t="n">
+        <v>443170.75</v>
+      </c>
       <c r="G117" s="101">
         <f>D117/F117-1</f>
         <v/>
@@ -9436,13 +9440,15 @@
         <v>959454.5677563855</v>
       </c>
       <c r="D118" s="100" t="n">
-        <v>45285981.58</v>
+        <v>7141.72</v>
       </c>
       <c r="E118" s="101">
         <f>D118/C118</f>
         <v/>
       </c>
-      <c r="F118" s="100" t="n"/>
+      <c r="F118" s="100" t="n">
+        <v>105089.22</v>
+      </c>
       <c r="G118" s="101">
         <f>D118/F118-1</f>
         <v/>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9346,14 +9346,14 @@
         <v/>
       </c>
       <c r="D115" s="100" t="n">
-        <v>570428.7899999999</v>
+        <v>264327.67</v>
       </c>
       <c r="E115" s="101">
         <f>D115/C115</f>
         <v/>
       </c>
       <c r="F115" s="100" t="n">
-        <v>696534.1799999999</v>
+        <v>738315.29</v>
       </c>
       <c r="G115" s="101">
         <f>D115/F115-1</f>
@@ -9378,14 +9378,14 @@
         <v>1705697.009344685</v>
       </c>
       <c r="D116" s="100" t="n">
-        <v>246072.77</v>
+        <v>79161.14999999999</v>
       </c>
       <c r="E116" s="101">
         <f>D116/C116</f>
         <v/>
       </c>
       <c r="F116" s="100" t="n">
-        <v>148274.21</v>
+        <v>360445.58</v>
       </c>
       <c r="G116" s="101">
         <f>D116/F116-1</f>
@@ -9409,14 +9409,14 @@
         <v>2665151.577101071</v>
       </c>
       <c r="D117" s="100" t="n">
-        <v>317214.3</v>
+        <v>180795.15</v>
       </c>
       <c r="E117" s="101">
         <f>D117/C117</f>
         <v/>
       </c>
       <c r="F117" s="100" t="n">
-        <v>443170.75</v>
+        <v>377869.71</v>
       </c>
       <c r="G117" s="101">
         <f>D117/F117-1</f>
@@ -9440,15 +9440,13 @@
         <v>959454.5677563855</v>
       </c>
       <c r="D118" s="100" t="n">
-        <v>7141.72</v>
+        <v>4371.37</v>
       </c>
       <c r="E118" s="101">
         <f>D118/C118</f>
         <v/>
       </c>
-      <c r="F118" s="100" t="n">
-        <v>105089.22</v>
-      </c>
+      <c r="F118" s="100" t="n"/>
       <c r="G118" s="101">
         <f>D118/F118-1</f>
         <v/>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -10318,25 +10318,22 @@
         </is>
       </c>
       <c r="C133" s="112" t="n">
-        <v>0</v>
+        <v>0.215072</v>
       </c>
       <c r="D133" s="112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="21">
-        <f>D133/C133</f>
-        <v/>
+        <v>0.33801</v>
+      </c>
+      <c r="E133" s="21" t="n">
+        <v>1.571614</v>
       </c>
       <c r="F133" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="22">
-        <f>E133-F133</f>
-        <v/>
-      </c>
-      <c r="H133" s="101">
-        <f>E133/F133</f>
-        <v/>
+        <v>2.037636278655495</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>-0.466022</v>
+      </c>
+      <c r="H133" s="101" t="n">
+        <v>0.771293</v>
       </c>
       <c r="I133" s="103" t="n">
         <v>5270625</v>
@@ -10357,20 +10354,17 @@
       <c r="D134" s="112" t="n">
         <v>0.0302</v>
       </c>
-      <c r="E134" s="21">
-        <f>D134/C134</f>
-        <v/>
+      <c r="E134" s="21" t="n">
+        <v>4.507463</v>
       </c>
       <c r="F134" s="21" t="n">
         <v>2.9061</v>
       </c>
-      <c r="G134" s="22">
-        <f>E134-F134</f>
-        <v/>
-      </c>
-      <c r="H134" s="101">
-        <f>E134/F134</f>
-        <v/>
+      <c r="G134" s="22" t="n">
+        <v>1.601363</v>
+      </c>
+      <c r="H134" s="101" t="n">
+        <v>1.551035</v>
       </c>
       <c r="I134" s="103" t="n">
         <v>1353257</v>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -10318,28 +10318,28 @@
         </is>
       </c>
       <c r="C133" s="112" t="n">
-        <v>0.215072</v>
+        <v>0.21209</v>
       </c>
       <c r="D133" s="112" t="n">
-        <v>0.33801</v>
+        <v>0.335456</v>
       </c>
       <c r="E133" s="21" t="n">
-        <v>1.571614</v>
+        <v>1.5817</v>
       </c>
       <c r="F133" s="21" t="n">
         <v>2.037636278655495</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>-0.466022</v>
+        <v>-0.456</v>
       </c>
       <c r="H133" s="101" t="n">
-        <v>0.771293</v>
+        <v>0.7762</v>
       </c>
       <c r="I133" s="103" t="n">
-        <v>5270625</v>
+        <v>7910743</v>
       </c>
       <c r="J133" s="103" t="n">
-        <v>2725288.33066</v>
+        <v>1491319</v>
       </c>
     </row>
     <row r="134">
@@ -10349,28 +10349,28 @@
         </is>
       </c>
       <c r="C134" s="112" t="n">
-        <v>0.0067</v>
+        <v>0.006752</v>
       </c>
       <c r="D134" s="112" t="n">
-        <v>0.0302</v>
+        <v>0.028434</v>
       </c>
       <c r="E134" s="21" t="n">
-        <v>4.507463</v>
+        <v>4.2111</v>
       </c>
       <c r="F134" s="21" t="n">
         <v>2.9061</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>1.601363</v>
+        <v>1.305</v>
       </c>
       <c r="H134" s="101" t="n">
-        <v>1.551035</v>
+        <v>1.449</v>
       </c>
       <c r="I134" s="103" t="n">
-        <v>1353257</v>
+        <v>5270625</v>
       </c>
       <c r="J134" s="103" t="n">
-        <v>725533.22905</v>
+        <v>2725288</v>
       </c>
     </row>
     <row r="136" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -10281,10 +10281,10 @@
     <row r="132" ht="13.5" customHeight="1">
       <c r="B132" s="84" t="n"/>
       <c r="C132" s="95" t="n">
-        <v>0.2109305926466908</v>
+        <v>0.2120896400537903</v>
       </c>
       <c r="D132" s="95" t="n">
-        <v>0.333069</v>
+        <v>0.335456</v>
       </c>
       <c r="E132" s="85" t="inlineStr">
         <is>
@@ -10305,10 +10305,10 @@
         </is>
       </c>
       <c r="I132" s="1" t="n">
-        <v>7848911.466666667</v>
+        <v>7910742.785714285</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>1469871.58898</v>
+        <v>1491319.224516</v>
       </c>
     </row>
     <row r="133">
@@ -10318,16 +10318,16 @@
         </is>
       </c>
       <c r="C133" s="112" t="n">
-        <v>0.21209</v>
+        <v>0.006752232719069173</v>
       </c>
       <c r="D133" s="112" t="n">
-        <v>0.335456</v>
+        <v>0.02843437961289845</v>
       </c>
       <c r="E133" s="21" t="n">
         <v>1.5817</v>
       </c>
       <c r="F133" s="21" t="n">
-        <v>2.037636278655495</v>
+        <v>2.9061</v>
       </c>
       <c r="G133" s="22" t="n">
         <v>-0.456</v>
@@ -10336,10 +10336,10 @@
         <v>0.7762</v>
       </c>
       <c r="I133" s="103" t="n">
-        <v>7910743</v>
+        <v>5270625</v>
       </c>
       <c r="J133" s="103" t="n">
-        <v>1491319</v>
+        <v>2725288.33066</v>
       </c>
     </row>
     <row r="134">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>32389627.70686</v>
+        <v>34975149.62313001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>31643223.77757</v>
+        <v>33850963.58139</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>35522514.17281207</v>
+        <v>38086530.63278449</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>35000000</v>
+        <v>37100000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>46036869.25590001</v>
+        <v>49619233.40631</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>53288833.82045999</v>
+        <v>56687345.14430998</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>65296920.63516492</v>
+        <v>70010054.9161336</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>66844327.6</v>
+        <v>71106215.3</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>5911715.114849999</v>
+        <v>6210733.969369999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>3735617.23936</v>
+        <v>3953414.42998</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>4668244.055898658</v>
+        <v>5005198.094125312</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>4807018.15389968</v>
+        <v>5067018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>38550501.94708</v>
+        <v>40986570.86557</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>36103787.69422</v>
+        <v>39410895.44554999</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>43531280.42344328</v>
+        <v>46673369.94408906</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>42022350</v>
+        <v>46808785</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>29962467.94621</v>
+        <v>31610855.76639</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>29040917.19023</v>
+        <v>31381136.05132</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>32648460.31758246</v>
+        <v>35005027.4580668</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>34200000</v>
+        <v>36200000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>22614057.90135</v>
+        <v>24159296.11852</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>26008759.14053</v>
+        <v>27740624.68211</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>30863082.72783095</v>
+        <v>33090781.24417684</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>31258269.39</v>
+        <v>33171057.52</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,40 +3943,40 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>97.93021553000001</v>
+        <v>107.60307687</v>
       </c>
       <c r="D46" s="108" t="n">
-        <v>100.814</v>
+        <v>110.766</v>
       </c>
       <c r="E46" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.971395</v>
+        <v>0.971445</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.028605</v>
+        <v>0.028555</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.793439</v>
+        <v>0.792044</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.813846</v>
+        <v>0.817427</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-2.0407</v>
+        <v>-2.5383</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.985509</v>
+        <v>0.98561</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.844546</v>
+        <v>0.848127</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>14.0963</v>
+        <v>13.74830000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.545478</v>
+        <v>0.536247</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.454522</v>
+        <v>0.463753</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.871382</v>
+        <v>0.8682609999999999</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.855704</v>
+        <v>0.854326</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.5678</v>
+        <v>1.3935</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949881</v>
+        <v>0.951398</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.886404</v>
+        <v>0.8850259999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.347700000000003</v>
+        <v>6.637200000000007</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>109.59882038</v>
+        <v>104.976746898</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>108.652</v>
+        <v>103.594</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916565</v>
+        <v>0.915717</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.083435</v>
+        <v>0.084283</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.756123</v>
+        <v>0.755937</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.7804489999999999</v>
+        <v>0.777734</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4326</v>
+        <v>-2.1797</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.75467</v>
+        <v>0.751426</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8111489999999999</v>
+        <v>0.8084339999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-5.647899999999993</v>
+        <v>-5.700799999999987</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>78.824133768</v>
+        <v>82.429839468</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>90.294</v>
+        <v>94.422</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872972</v>
+        <v>0.872994</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127028</v>
+        <v>0.127006</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.811846</v>
+        <v>0.810068</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.826993</v>
+        <v>0.827279</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-1.5147</v>
+        <v>-1.7211</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.873203</v>
+        <v>0.870824</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8576929999999998</v>
+        <v>0.8579789999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.551000000000016</v>
+        <v>1.284500000000008</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820505</v>
+        <v>0.820496</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179495</v>
+        <v>0.179504</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.884324</v>
+        <v>0.883811</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.831376</v>
+        <v>0.832088</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.2948</v>
+        <v>5.1723</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887052</v>
+        <v>0.887315</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.862076</v>
+        <v>0.8627879999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.497600000000006</v>
+        <v>2.452700000000007</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9442551200979122</v>
+        <v>0.9427468344236526</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9351252719748095</v>
+        <v>0.9332225462432315</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9385070529208377</v>
+        <v>0.9372843585708187</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8904571310876348</v>
+        <v>0.8898607515239287</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.933685712972067</v>
+        <v>0.9320403064061903</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8888831732323637</v>
+        <v>0.8883333799460382</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9779898468577517</v>
+        <v>0.9772636330854493</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8722023115804697</v>
+        <v>0.872594288391489</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.962906447794792</v>
+        <v>0.9577927280300074</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8449899596660958</v>
+        <v>0.8426085357633553</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9475576301941477</v>
+        <v>0.945974185455224</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8800287196118829</v>
+        <v>0.8788971925389848</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9430572607356902</v>
+        <v>0.9416109877180318</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8852997933328283</v>
+        <v>0.8845619506364751</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2109305926466908</v>
+        <v>0.2100804882819329</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.333069</v>
+        <v>0.335974</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7848911.466666667</v>
+        <v>7788367.25</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1469871.58898</v>
+        <v>1487982.675145</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.006752232719069173</v>
+        <v>0.00677195226220127</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02843437961289845</v>
+        <v>0.02880624824907791</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>5270625</v>
+        <v>5621606</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>2725288.33066</v>
+        <v>2962708.56432</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>34975149.62313001</v>
+        <v>41171977.66142999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>33850963.58139</v>
+        <v>39870920.72767</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>38086530.63278449</v>
+        <v>44282217.04154427</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>37100000</v>
+        <v>44600000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>49619233.40631</v>
+        <v>58418083.24780001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>56687345.14430998</v>
+        <v>65883708.92365</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>70010054.9161336</v>
+        <v>81398867.14223428</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>71106215.3</v>
+        <v>82641342.7</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>6210733.969369999</v>
+        <v>7043379.949359999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>3953414.42998</v>
+        <v>4519848.26041</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>5005198.094125312</v>
+        <v>5819413.442430859</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>5067018.15389968</v>
+        <v>5847018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>40986570.86557</v>
+        <v>50217161.58193</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>39410895.44554999</v>
+        <v>45786525.72287001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>46673369.94408906</v>
+        <v>54265911.42815619</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>46808785</v>
+        <v>54575872</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>31610855.76639</v>
+        <v>37166308.61001</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>31381136.05132</v>
+        <v>35875548.66118</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>35005027.4580668</v>
+        <v>40699433.57111714</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>36200000</v>
+        <v>41800000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>24159296.11852</v>
+        <v>29036981.66141</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>27740624.68211</v>
+        <v>32989934.38993</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>33090781.24417684</v>
+        <v>38473789.36288719</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>33171057.52</v>
+        <v>40002249.98</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,40 +3943,40 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>107.60307687</v>
+        <v>116.46168</v>
       </c>
       <c r="D46" s="108" t="n">
-        <v>110.766</v>
+        <v>120</v>
       </c>
       <c r="E46" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.971445</v>
+        <v>0.970514</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.028555</v>
+        <v>0.029486</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792044</v>
+        <v>0.792861</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.817427</v>
+        <v>0.823144</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-2.5383</v>
+        <v>-3.0283</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.98561</v>
+        <v>0.980118</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.848127</v>
+        <v>0.853844</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>13.74830000000001</v>
+        <v>12.62739999999999</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.536247</v>
+        <v>0.547494</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.463753</v>
+        <v>0.452506</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.8682609999999999</v>
+        <v>0.851843</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.854326</v>
+        <v>0.849729</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.3935</v>
+        <v>0.2114</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.951398</v>
+        <v>0.951146</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8850259999999999</v>
+        <v>0.8804289999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.637200000000007</v>
+        <v>7.071700000000007</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>104.976746898</v>
+        <v>97.47265964</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>103.594</v>
+        <v>95.402</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.915717</v>
+        <v>0.91582</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.084283</v>
+        <v>0.08418</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.755937</v>
+        <v>0.757598</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.777734</v>
+        <v>0.775299</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.1797</v>
+        <v>-1.7701</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.751426</v>
+        <v>0.74193</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8084339999999999</v>
+        <v>0.8059989999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-5.700799999999987</v>
+        <v>-6.406899999999993</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>82.429839468</v>
+        <v>89.49326068799999</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>94.422</v>
+        <v>102.616</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872994</v>
+        <v>0.8721179999999999</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127006</v>
+        <v>0.127882</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.810068</v>
+        <v>0.80793</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.827279</v>
+        <v>0.829238</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-1.7211</v>
+        <v>-2.1308</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870824</v>
+        <v>0.87088</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8579789999999999</v>
+        <v>0.859938</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.284500000000008</v>
+        <v>1.094200000000001</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820496</v>
+        <v>0.820179</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179504</v>
+        <v>0.179821</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.883811</v>
+        <v>0.886393</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.832088</v>
+        <v>0.835625</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.1723</v>
+        <v>5.0768</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887315</v>
+        <v>0.887994</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8627879999999999</v>
+        <v>0.8663249999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.452700000000007</v>
+        <v>2.166900000000012</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9427468344236526</v>
+        <v>0.9391932047017469</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9332225462432315</v>
+        <v>0.9300424722153577</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9372843585708187</v>
+        <v>0.9342072505209006</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8898607515239287</v>
+        <v>0.8890427547929984</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9320403064061903</v>
+        <v>0.9281154743709659</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8883333799460382</v>
+        <v>0.8884953019252709</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9772636330854493</v>
+        <v>0.974922644430219</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.872594288391489</v>
+        <v>0.8723162364702726</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9577927280300074</v>
+        <v>0.9457953338027764</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8426085357633553</v>
+        <v>0.8367295224048984</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.945974185455224</v>
+        <v>0.9421029888053504</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8788971925389848</v>
+        <v>0.879677870232397</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9416109877180318</v>
+        <v>0.9380595280669098</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8845619506364751</v>
+        <v>0.884070603110812</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1426.133333333333</v>
+        <v>1417.578947368421</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7102655198204936</v>
+        <v>0.7105145912229895</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894085</v>
+        <v>0.89395</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885304</v>
+        <v>0.8848</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.7725321888412017</v>
+        <v>0.8059210526315789</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0674717790657853</v>
+        <v>0.0712106478980485</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>113.6</v>
+        <v>115.4736842105263</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2488262910798122</v>
+        <v>0.2525068368277119</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.726978</v>
+        <v>0.729419</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1528878822197055</v>
+        <v>0.1462979482604817</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>333</v>
+        <v>323.9473684210527</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7187187187187187</v>
+        <v>0.7166531275385865</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.885275</v>
+        <v>0.884624</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.884537</v>
+        <v>0.8840479999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.056609623015873</v>
+        <v>0.0537193203272498</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>881.2</v>
+        <v>879.578947368421</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8033741867150855</v>
+        <v>0.804571565342269</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.911267</v>
+        <v>0.912312</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.890388</v>
+        <v>0.890002</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.7831325301204819</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.0750439437519974</v>
+        <v>0.08231989555722589</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>2</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>95.66666666666667</v>
+        <v>96.15789473684211</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3700348432055749</v>
+        <v>0.378215654077723</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.832282</v>
+        <v>0.833014</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.780199</v>
+        <v>0.786158</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7873,7 +7873,7 @@
         <v/>
       </c>
       <c r="K87" s="104" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="104" t="n">
         <v>0.8082191781</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0195141377937077</v>
+        <v>0.0173446862188584</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2100804882819329</v>
+        <v>0.2083237677029555</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.335974</v>
+        <v>0.332953</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7788367.25</v>
+        <v>7796653.842105263</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1487982.675145</v>
+        <v>1476822.691801</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00677195226220127</v>
+        <v>0.00665428956107793</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02880624824907791</v>
+        <v>0.02782999520629043</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>5621606</v>
+        <v>6588703</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>2962708.56432</v>
+        <v>3385945.54841</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>41171977.66142999</v>
+        <v>43289792.78181999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>39870920.72767</v>
+        <v>42442675.40130001</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>44282217.04154427</v>
+        <v>46425214.86260591</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>44600000</v>
+        <v>46700000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>58418083.24780001</v>
+        <v>61153197.11276</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>65883708.92365</v>
+        <v>69851125.45231</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>81398867.14223428</v>
+        <v>85338091.65664922</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>82641342.7</v>
+        <v>87618566.3</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7043379.949359999</v>
+        <v>7262340.18936</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>4519848.26041</v>
+        <v>4870833.2415</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>5819413.442430859</v>
+        <v>6101038.689768548</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>5847018.15389968</v>
+        <v>6107018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>50217161.58193</v>
+        <v>53139231.56896</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>45786525.72287001</v>
+        <v>48081451.18179001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>54265911.42815619</v>
+        <v>56892061.10443281</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>54575872</v>
+        <v>57308811</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>37166308.61001</v>
+        <v>38648926.94507</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>35875548.66118</v>
+        <v>37426251.35981</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>40699433.57111714</v>
+        <v>42669045.82832461</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>41800000</v>
+        <v>43600000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>29036981.66141</v>
+        <v>30363680.32967999</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>32989934.38993</v>
+        <v>34599061.04399</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>38473789.36288719</v>
+        <v>40335693.58270753</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>40002249.98</v>
+        <v>41783216.00000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2083237677029555</v>
+        <v>0.2069161860978783</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.332953</v>
+        <v>0.331403</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7796653.842105263</v>
+        <v>7726440.1</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1476822.691801</v>
+        <v>1463587.648948</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>43289792.78181999</v>
+        <v>45589046.04950999</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>42442675.40130001</v>
+        <v>44748936.31879</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>46425214.86260591</v>
+        <v>48732922.6058565</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>46700000</v>
+        <v>48800000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>61153197.11276</v>
+        <v>64286928.90509001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>69851125.45231</v>
+        <v>73099594.72197999</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>85338091.65664922</v>
+        <v>89580083.33063722</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>87618566.3</v>
+        <v>91691966.89999999</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7262340.18936</v>
+        <v>7600357.68936</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>4870833.2415</v>
+        <v>5177671.695250001</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6101038.689768548</v>
+        <v>6404309.53661154</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6107018.15389968</v>
+        <v>6457018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>53139231.56896</v>
+        <v>55938957.81296</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>48081451.18179001</v>
+        <v>50608246.44949001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>56892061.10443281</v>
+        <v>59720055.55375814</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>57308811</v>
+        <v>60117581</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>38648926.94507</v>
+        <v>41020829.74684</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>37426251.35981</v>
+        <v>39068688.49191999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>42669045.82832461</v>
+        <v>44790041.66531861</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>43600000</v>
+        <v>45400000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>30363680.32967999</v>
+        <v>31849970.08093</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>34599061.04399</v>
+        <v>36672628.1319</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>40335693.58270753</v>
+        <v>42340702.98730963</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>41783216.00000001</v>
+        <v>43728188.65000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.46168</v>
+        <v>116.50236</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970514</v>
+        <v>0.970853</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029486</v>
+        <v>0.029147</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792861</v>
+        <v>0.790543</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.823144</v>
+        <v>0.825946</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-3.0283</v>
+        <v>-3.5403</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.980118</v>
+        <v>0.981071</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.853844</v>
+        <v>0.8566459999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.62739999999999</v>
+        <v>12.44250000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.547494</v>
+        <v>0.559321</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.452506</v>
+        <v>0.440679</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.851843</v>
+        <v>0.856669</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.849729</v>
+        <v>0.8493889999999999</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.2114</v>
+        <v>0.728</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.951146</v>
+        <v>0.949338</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8804289999999999</v>
+        <v>0.880089</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.071700000000007</v>
+        <v>6.924900000000008</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>97.47265964</v>
+        <v>109.828543758</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>95.402</v>
+        <v>108.906</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.91582</v>
+        <v>0.916843</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08418</v>
+        <v>0.08315699999999999</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.757598</v>
+        <v>0.753799</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.775299</v>
+        <v>0.7782520000000001</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-1.7701</v>
+        <v>-2.4453</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.74193</v>
+        <v>0.736854</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8059989999999999</v>
+        <v>0.8089519999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-6.406899999999993</v>
+        <v>-7.209799999999987</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>89.49326068799999</v>
+        <v>90.611526224</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>102.616</v>
+        <v>103.828</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.8721179999999999</v>
+        <v>0.872708</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127882</v>
+        <v>0.127292</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.80793</v>
+        <v>0.807859</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829238</v>
+        <v>0.829773</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1308</v>
+        <v>-2.1914</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.87088</v>
+        <v>0.870929</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.859938</v>
+        <v>0.8604729999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.094200000000001</v>
+        <v>1.045600000000007</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.820179</v>
+        <v>0.819945</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.179821</v>
+        <v>0.180055</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.886393</v>
+        <v>0.887614</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.835625</v>
+        <v>0.8361189999999999</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.0768</v>
+        <v>5.1495</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.887994</v>
+        <v>0.8876309999999999</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8663249999999999</v>
+        <v>0.866819</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.166900000000012</v>
+        <v>2.081199999999995</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9391932047017469</v>
+        <v>0.9377664531082669</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9300424722153577</v>
+        <v>0.9295606008002918</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9342072505209006</v>
+        <v>0.9331097747525502</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8890427547929984</v>
+        <v>0.889161285998024</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9281154743709659</v>
+        <v>0.9262097744348601</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8884953019252709</v>
+        <v>0.8903262920570877</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.974922644430219</v>
+        <v>0.9759493574653033</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8723162364702726</v>
+        <v>0.874971963372827</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9457953338027764</v>
+        <v>0.944278190056519</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8367295224048984</v>
+        <v>0.8335662778560988</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9421029888053504</v>
+        <v>0.9420106884871495</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.879677870232397</v>
+        <v>0.8797788230581509</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9380595280669098</v>
+        <v>0.9372072413951775</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884070603110812</v>
+        <v>0.884462242152963</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1417.578947368421</v>
+        <v>1415.35</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7105145912229895</v>
+        <v>0.7109195605327304</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.89395</v>
+        <v>0.894324</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.8848</v>
+        <v>0.885115</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8059210526315789</v>
+        <v>0.8081761006289307</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0712106478980485</v>
+        <v>0.0719065675122228</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>115.4736842105263</v>
+        <v>115.85</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2525068368277119</v>
+        <v>0.2537764350453172</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.729419</v>
+        <v>0.730587</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1462979482604817</v>
+        <v>0.1457627118644068</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>323.9473684210527</v>
+        <v>322.25</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7166531275385865</v>
+        <v>0.7154383242823894</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.884624</v>
+        <v>0.884232</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8840479999999999</v>
+        <v>0.8841869999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9375</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0537193203272498</v>
+        <v>0.0524923654026499</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>879.578947368421</v>
+        <v>878.6</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.804571565342269</v>
+        <v>0.8057136353289324</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.912312</v>
+        <v>0.913868</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.890002</v>
+        <v>0.891497</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7808764940239044</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.08231989555722589</v>
+        <v>0.0839250886691717</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.894736842105263</v>
+        <v>1.85</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.75</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2545454545454545</v>
+        <v>0.2456140350877193</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.15789473684211</v>
+        <v>96.3</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.378215654077723</v>
+        <v>0.3795430944963655</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.833014</v>
+        <v>0.834858</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.786158</v>
+        <v>0.787304</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7873,7 +7873,7 @@
         <v/>
       </c>
       <c r="K87" s="104" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="L87" s="104" t="n">
         <v>0.8082191781</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0173446862188584</v>
+        <v>0.0167714884696017</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2069161860978783</v>
+        <v>0.2064424084151716</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331403</v>
+        <v>0.332475</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7726440.1</v>
+        <v>7707249.476190476</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1463587.648948</v>
+        <v>1467249.25156</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00665428956107793</v>
+        <v>0.00673394578260548</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02782999520629043</v>
+        <v>0.02802774511698452</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>6588703</v>
+        <v>7351980</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3385945.54841</v>
+        <v>3749215.65042</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>45589046.04950999</v>
+        <v>47525575.17379998</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>44748936.31879</v>
+        <v>46784690.49070001</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>48732922.6058565</v>
+        <v>51040630.3491071</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>48800000</v>
+        <v>50900000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>64286928.90509001</v>
+        <v>67149527.50237</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>73099594.72197999</v>
+        <v>76362319.94632</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>89580083.33063722</v>
+        <v>93822075.00462522</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>91691966.89999999</v>
+        <v>95784903.69999999</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7600357.68936</v>
+        <v>7852956.128949999</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5177671.695250001</v>
+        <v>5373553.104139999</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6404309.53661154</v>
+        <v>6707580.383454532</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6457018.15389968</v>
+        <v>6717018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>55938957.81296</v>
+        <v>59910928.16398</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>50608246.44949001</v>
+        <v>52905814.67994001</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>59720055.55375814</v>
+        <v>62548050.00308348</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>60117581</v>
+        <v>64104255</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>41020829.74684</v>
+        <v>42452329.48069</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>39068688.49191999</v>
+        <v>40679482.70381999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>44790041.66531861</v>
+        <v>46911037.50231261</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>45400000</v>
+        <v>47200000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>31849970.08093</v>
+        <v>33202502.2384</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>36672628.1319</v>
+        <v>38581436.85924</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>42340702.98730963</v>
+        <v>44345712.39191172</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>43728188.65000001</v>
+        <v>45509154.67000001</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.50236</v>
+        <v>116.47248</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970853</v>
+        <v>0.970604</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029147</v>
+        <v>0.029396</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.790543</v>
+        <v>0.790282</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.825946</v>
+        <v>0.83053</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-3.5403</v>
+        <v>-4.0248</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.981071</v>
+        <v>0.981855</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8566459999999999</v>
+        <v>0.8612299999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.44250000000001</v>
+        <v>12.06250000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.559321</v>
+        <v>0.548767</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.440679</v>
+        <v>0.451233</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.856669</v>
+        <v>0.857147</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.8493889999999999</v>
+        <v>0.8485</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.728</v>
+        <v>0.8647</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949338</v>
+        <v>0.950507</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.880089</v>
+        <v>0.8791999999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>6.924900000000008</v>
+        <v>7.130700000000019</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>109.828543758</v>
+        <v>110.34237613</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>108.906</v>
+        <v>109.466</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916843</v>
+        <v>0.916805</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08315699999999999</v>
+        <v>0.08319500000000001</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.753799</v>
+        <v>0.753354</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.7782520000000001</v>
+        <v>0.778087</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4453</v>
+        <v>-2.4733</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.736854</v>
+        <v>0.736253</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8089519999999999</v>
+        <v>0.8087869999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.209799999999987</v>
+        <v>-7.253399999999999</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>90.611526224</v>
+        <v>89.945364064</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>103.828</v>
+        <v>102.944</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.872708</v>
+        <v>0.873731</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.127292</v>
+        <v>0.126269</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.807859</v>
+        <v>0.808609</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829773</v>
+        <v>0.830081</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1914</v>
+        <v>-2.1472</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870929</v>
+        <v>0.870567</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8604729999999999</v>
+        <v>0.8607809999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1.045600000000007</v>
+        <v>0.9786000000000143</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819945</v>
+        <v>0.819897</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180055</v>
+        <v>0.180103</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887614</v>
+        <v>0.8876540000000001</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.8361189999999999</v>
+        <v>0.8362540000000001</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.1495</v>
+        <v>5.14</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.8876309999999999</v>
+        <v>0.886872</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.866819</v>
+        <v>0.8669539999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.081199999999995</v>
+        <v>1.991800000000012</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9377664531082669</v>
+        <v>0.9383307347157092</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9295606008002918</v>
+        <v>0.92959908861528</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9331097747525502</v>
+        <v>0.9324869092347707</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.889161285998024</v>
+        <v>0.8893768496515304</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9262097744348601</v>
+        <v>0.925484107726843</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8903262920570877</v>
+        <v>0.8903021331892945</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9759493574653033</v>
+        <v>0.976732113881141</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.874971963372827</v>
+        <v>0.8759961244614934</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.944278190056519</v>
+        <v>0.9436485456006595</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8335662778560988</v>
+        <v>0.832181997564462</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9420106884871495</v>
+        <v>0.9408606658083472</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8797788230581509</v>
+        <v>0.879219019959161</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9372072413951775</v>
+        <v>0.9365345017520862</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884462242152963</v>
+        <v>0.8844618193862247</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1415.35</v>
+        <v>1412.272727272727</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7109195605327304</v>
+        <v>0.7101383971676859</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894324</v>
+        <v>0.894188</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885115</v>
+        <v>0.885545</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8081761006289307</v>
+        <v>0.8211143695014663</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.0719065675122228</v>
+        <v>0.073307413862448</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>115.85</v>
+        <v>116.5909090909091</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2537764350453172</v>
+        <v>0.2514619883040936</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.730587</v>
+        <v>0.729693</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1457627118644068</v>
+        <v>0.1486902927580894</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>322.25</v>
+        <v>319.3181818181818</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7154383242823894</v>
+        <v>0.7117437722419929</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.884232</v>
+        <v>0.883387</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8841869999999999</v>
+        <v>0.8843569999999999</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9491525423728814</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0524923654026499</v>
+        <v>0.0509589282955574</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>878.6</v>
+        <v>877.5909090909091</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8057136353289324</v>
+        <v>0.8066504376650956</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.913868</v>
+        <v>0.914772</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.891497</v>
+        <v>0.89377</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7808764940239044</v>
+        <v>0.7970479704797048</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.0839250886691717</v>
+        <v>0.08662957041997429</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.85</v>
+        <v>1.772727272727273</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.3</v>
+        <v>96.54545454545455</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3795430944963655</v>
+        <v>0.3799435028248588</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.834858</v>
+        <v>0.836784</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.787304</v>
+        <v>0.786184</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0167714884696017</v>
+        <v>0.0157823129251701</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2064424084151716</v>
+        <v>0.2056574404662959</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.332475</v>
+        <v>0.331837</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7707249.476190476</v>
+        <v>7668654.636363637</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1467249.25156</v>
+        <v>1455233.708801</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.00673394578260548</v>
+        <v>0.006769477479549126</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02802774511698452</v>
+        <v>0.02799087293035355</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>7351980</v>
+        <v>7738094</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3749215.65042</v>
+        <v>3900708.87635</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>47525575.17379998</v>
+        <v>54735893.93229</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>46784690.49070001</v>
+        <v>52759033.71797</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>51040630.3491071</v>
+        <v>57963753.57885889</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>50900000</v>
+        <v>58000000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>67149527.50237</v>
+        <v>76061236.11712998</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>76362319.94632</v>
+        <v>84967378.18013997</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>93822075.00462522</v>
+        <v>106548050.0265892</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>95784903.69999999</v>
+        <v>106576302.6</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>7852956.128949999</v>
+        <v>8807212.498960001</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5373553.104139999</v>
+        <v>5856652.913499999</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>6707580.383454532</v>
+        <v>7617392.923983509</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>6717018.15389968</v>
+        <v>7737018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>59910928.16398</v>
+        <v>67122608.46252</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>52905814.67994001</v>
+        <v>59023804.94531002</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>62548050.00308348</v>
+        <v>71032033.3510595</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>64104255</v>
+        <v>71753046</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>42452329.48069</v>
+        <v>49268004.31358999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>40679482.70381999</v>
+        <v>44587547.41755999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>46911037.50231261</v>
+        <v>53274025.01329462</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>47200000</v>
+        <v>54300000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>33202502.2384</v>
+        <v>37541787.8267</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>38581436.85924</v>
+        <v>43771413.76890001</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>44345712.39191172</v>
+        <v>50360740.60571799</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>45509154.67000001</v>
+        <v>51078450.14000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.47248</v>
+        <v>116.445</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970604</v>
+        <v>0.970375</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029396</v>
+        <v>0.029625</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.790282</v>
+        <v>0.792167</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.83053</v>
+        <v>0.837401</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.0248</v>
+        <v>-4.5234</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.981855</v>
+        <v>0.983659</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8612299999999999</v>
+        <v>0.8681009999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>12.06250000000001</v>
+        <v>11.5558</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.548767</v>
+        <v>0.546643</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.451233</v>
+        <v>0.453357</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.857147</v>
+        <v>0.8603150000000001</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.8485</v>
+        <v>0.846844</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.8647</v>
+        <v>1.3471</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.950507</v>
+        <v>0.9500960000000001</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8791999999999999</v>
+        <v>0.8775439999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.130700000000019</v>
+        <v>7.255200000000016</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4037,40 +4037,40 @@
         </is>
       </c>
       <c r="C48" s="107" t="n">
-        <v>110.34237613</v>
+        <v>120</v>
       </c>
       <c r="D48" s="108" t="n">
-        <v>109.466</v>
+        <v>120</v>
       </c>
       <c r="E48" s="108" t="n">
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.916805</v>
+        <v>0.91769</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08319500000000001</v>
+        <v>0.08230999999999999</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.753354</v>
+        <v>0.747212</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.778087</v>
+        <v>0.77783</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-2.4733</v>
+        <v>-3.0618</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.736253</v>
+        <v>0.7315</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.8087869999999999</v>
+        <v>0.80853</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.253399999999999</v>
+        <v>-7.702999999999989</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>89.945364064</v>
+        <v>88.3721412</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>102.944</v>
+        <v>100.916</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.873731</v>
+        <v>0.8757</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.126269</v>
+        <v>0.1243</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.808609</v>
+        <v>0.809462</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.830081</v>
+        <v>0.82992</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.1472</v>
+        <v>-2.0458</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.870567</v>
+        <v>0.869747</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8607809999999999</v>
+        <v>0.8606199999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.9786000000000143</v>
+        <v>0.912700000000001</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819897</v>
+        <v>0.8197950000000001</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180103</v>
+        <v>0.180205</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.8876540000000001</v>
+        <v>0.887869</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.8362540000000001</v>
+        <v>0.836189</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.14</v>
+        <v>5.168</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.886872</v>
+        <v>0.8867350000000001</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8669539999999999</v>
+        <v>0.8668889999999999</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1.991800000000012</v>
+        <v>1.984600000000015</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9383307347157092</v>
+        <v>0.9400249378581307</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.92959908861528</v>
+        <v>0.9279819424053481</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9324869092347707</v>
+        <v>0.9307705605273685</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8893768496515304</v>
+        <v>0.8890346641582334</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.925484107726843</v>
+        <v>0.9233301685310997</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8903021331892945</v>
+        <v>0.8912813922486551</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.976732113881141</v>
+        <v>0.9787141069107258</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8759961244614934</v>
+        <v>0.8791324787668708</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9436485456006595</v>
+        <v>0.945126033063153</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.832181997564462</v>
+        <v>0.82895538490589</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9408606658083472</v>
+        <v>0.9405040502356217</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.879219019959161</v>
+        <v>0.8795221304927711</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9365345017520862</v>
+        <v>0.9354874739169118</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8844618193862247</v>
+        <v>0.8845984761544614</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1412.272727272727</v>
+        <v>1408.52</v>
       </c>
       <c r="D81" s="104" t="n">
-        <v>0.7101383971676859</v>
+        <v>0.7095958878823162</v>
       </c>
       <c r="E81" s="104" t="n">
-        <v>0.894188</v>
+        <v>0.894176</v>
       </c>
       <c r="F81" s="104" t="n">
         <v>0.8146325152</v>
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="H81" s="104" t="n">
-        <v>0.885545</v>
+        <v>0.885266</v>
       </c>
       <c r="I81" s="104" t="n">
         <v>0.8207995184</v>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
       <c r="K81" s="104" t="n">
-        <v>0.8211143695014663</v>
+        <v>0.8283378746594005</v>
       </c>
       <c r="L81" s="104" t="n">
         <v>0.8082191781</v>
@@ -7553,7 +7553,7 @@
         <v/>
       </c>
       <c r="N81" s="104" t="n">
-        <v>0.073307413862448</v>
+        <v>0.074526339061877</v>
       </c>
       <c r="O81" s="104" t="n">
         <v>0.0611152139</v>
@@ -7570,13 +7570,13 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>116.5909090909091</v>
+        <v>116.8</v>
       </c>
       <c r="D82" s="104" t="n">
-        <v>0.2514619883040936</v>
+        <v>0.2503424657534247</v>
       </c>
       <c r="E82" s="104" t="n">
-        <v>0.729693</v>
+        <v>0.731436</v>
       </c>
       <c r="F82" s="104" t="n">
         <v>0.7556221149</v>
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="N82" s="104" t="n">
-        <v>0.1486902927580894</v>
+        <v>0.1481985044187627</v>
       </c>
       <c r="O82" s="104" t="n">
         <v>0.0611152139</v>
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>319.3181818181818</v>
+        <v>316.12</v>
       </c>
       <c r="D83" s="104" t="n">
-        <v>0.7117437722419929</v>
+        <v>0.7089712767303556</v>
       </c>
       <c r="E83" s="104" t="n">
-        <v>0.883387</v>
+        <v>0.882393</v>
       </c>
       <c r="F83" s="104" t="n">
         <v>0.8066</v>
@@ -7641,7 +7641,7 @@
         <v/>
       </c>
       <c r="H83" s="104" t="n">
-        <v>0.8843569999999999</v>
+        <v>0.88357</v>
       </c>
       <c r="I83" s="104" t="n">
         <v>0.8207995184</v>
@@ -7651,7 +7651,7 @@
         <v/>
       </c>
       <c r="K83" s="104" t="n">
-        <v>0.9491525423728814</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="L83" s="104" t="n">
         <v>0.8082191781</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="N83" s="104" t="n">
-        <v>0.0509589282955574</v>
+        <v>0.0477760119292876</v>
       </c>
       <c r="O83" s="104" t="n">
         <v>0.0611152139</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>877.5909090909091</v>
+        <v>876.72</v>
       </c>
       <c r="D84" s="104" t="n">
-        <v>0.8066504376650956</v>
+        <v>0.8070535632813213</v>
       </c>
       <c r="E84" s="104" t="n">
-        <v>0.914772</v>
+        <v>0.916081</v>
       </c>
       <c r="F84" s="104" t="n">
         <v>0.8078</v>
@@ -7694,7 +7694,7 @@
         <v/>
       </c>
       <c r="H84" s="104" t="n">
-        <v>0.89377</v>
+        <v>0.896254</v>
       </c>
       <c r="I84" s="104" t="n">
         <v>0.8207995184</v>
@@ -7704,7 +7704,7 @@
         <v/>
       </c>
       <c r="K84" s="104" t="n">
-        <v>0.7970479704797048</v>
+        <v>0.8054607508532423</v>
       </c>
       <c r="L84" s="104" t="n">
         <v>0.8082191781</v>
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="N84" s="104" t="n">
-        <v>0.08662957041997429</v>
+        <v>0.0891388851887284</v>
       </c>
       <c r="O84" s="104" t="n">
         <v>0.0611152139</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1.772727272727273</v>
+        <v>1.68</v>
       </c>
       <c r="D86" s="104" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E86" s="104" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v/>
       </c>
       <c r="N86" s="104" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="O86" s="104" t="n">
         <v>0.0611152139</v>
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>96.54545454545455</v>
+        <v>96.8</v>
       </c>
       <c r="D87" s="104" t="n">
-        <v>0.3799435028248588</v>
+        <v>0.381404958677686</v>
       </c>
       <c r="E87" s="104" t="n">
-        <v>0.836784</v>
+        <v>0.847162</v>
       </c>
       <c r="F87" s="104" t="n">
         <v>0.8087257009</v>
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="H87" s="104" t="n">
-        <v>0.786184</v>
+        <v>0.789895</v>
       </c>
       <c r="I87" s="104" t="n">
         <v>0.8207995184</v>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
       <c r="N87" s="104" t="n">
-        <v>0.0157823129251701</v>
+        <v>0.0181731229076997</v>
       </c>
       <c r="O87" s="104" t="n">
         <v>0.0611152139</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2056574404662959</v>
+        <v>0.2033793401415985</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331837</v>
+        <v>0.331626</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7668654.636363637</v>
+        <v>7621041.6</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1455233.708801</v>
+        <v>1463091.527252</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.006769477479549126</v>
+        <v>0.007090098790202326</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02799087293035355</v>
+        <v>0.02881851247498287</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>7738094</v>
+        <v>9252265</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>3900708.87635</v>
+        <v>4576725.16585</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>54735893.93229</v>
+        <v>56999284.90107001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>52759033.71797</v>
+        <v>55034458.62962</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>57963753.57885889</v>
+        <v>60271461.32210948</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>58000000</v>
+        <v>60500000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>76061236.11712998</v>
+        <v>79575002.75239</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>84967378.18013997</v>
+        <v>88621756.21001998</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>106548050.0265892</v>
+        <v>110790041.7005772</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>106576302.6</v>
+        <v>111158802.7</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>8807212.498960001</v>
+        <v>9133109.288960002</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>5856652.913499999</v>
+        <v>6257675.0648</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>7617392.923983509</v>
+        <v>7920663.770826501</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>7737018.15389968</v>
+        <v>7997018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>67122608.46252</v>
+        <v>69431574.30306</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>59023804.94531002</v>
+        <v>60801537.63507</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>71032033.3510595</v>
+        <v>73860027.80038483</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>71753046</v>
+        <v>74144241</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>49268004.31358999</v>
+        <v>51610245.77668999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>44587547.41755999</v>
+        <v>45753281.23078001</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>53274025.01329462</v>
+        <v>55395020.85028862</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>54300000</v>
+        <v>56100000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>37541787.8267</v>
+        <v>39250344.41577</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>43771413.76890001</v>
+        <v>45520419.64603</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>50360740.60571799</v>
+        <v>52365750.01032007</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>51078450.14000002</v>
+        <v>52859416.16000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.445</v>
+        <v>116.38536</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.970375</v>
+        <v>0.969878</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.029625</v>
+        <v>0.030122</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792167</v>
+        <v>0.792257</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.837401</v>
+        <v>0.838044</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.5234</v>
+        <v>-4.5787</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.983659</v>
+        <v>0.9810990000000001</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.8681009999999999</v>
+        <v>0.868744</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>11.5558</v>
+        <v>11.2355</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.546643</v>
+        <v>0.548602</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.453357</v>
+        <v>0.451398</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.8603150000000001</v>
+        <v>0.860413</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.846844</v>
+        <v>0.845364</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.3471</v>
+        <v>1.5049</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.9500960000000001</v>
+        <v>0.949968</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.8775439999999999</v>
+        <v>0.876064</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.255200000000016</v>
+        <v>7.3904</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4046,31 +4046,31 @@
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.91769</v>
+        <v>0.917855</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.08230999999999999</v>
+        <v>0.082145</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.747212</v>
+        <v>0.745633</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.77783</v>
+        <v>0.776695</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-3.0618</v>
+        <v>-3.1062</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.7315</v>
+        <v>0.729692</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.80853</v>
+        <v>0.807395</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.702999999999989</v>
+        <v>-7.770299999999992</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>88.3721412</v>
+        <v>87.87192760000001</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>100.916</v>
+        <v>100.37</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.8757</v>
+        <v>0.87548</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.1243</v>
+        <v>0.12452</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.809462</v>
+        <v>0.809492</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.82992</v>
+        <v>0.829677</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.0458</v>
+        <v>-2.0185</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.869747</v>
+        <v>0.86995</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8606199999999999</v>
+        <v>0.8603769999999998</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.912700000000001</v>
+        <v>0.9573000000000178</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.8197950000000001</v>
+        <v>0.819715</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180205</v>
+        <v>0.180285</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887869</v>
+        <v>0.887647</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.836189</v>
+        <v>0.835376</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.168</v>
+        <v>5.2271</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.8867350000000001</v>
+        <v>0.886501</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.8668889999999999</v>
+        <v>0.866076</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1.984600000000015</v>
+        <v>2.042500000000004</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9400249378581307</v>
+        <v>0.9397703933271144</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9279819424053481</v>
+        <v>0.9279951388178347</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9307705605273685</v>
+        <v>0.9301326499269785</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8890346641582334</v>
+        <v>0.8892783347494847</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.9233301685310997</v>
+        <v>0.922493958562407</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8912813922486551</v>
+        <v>0.8914821215654777</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9787141069107258</v>
+        <v>0.9792712353493512</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8791324787668708</v>
+        <v>0.8798879221523218</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.945126033063153</v>
+        <v>0.9459716828904183</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.82895538490589</v>
+        <v>0.8280673271363532</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9405040502356217</v>
+        <v>0.9405248187055548</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8795221304927711</v>
+        <v>0.8791349788351291</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.9354874739169118</v>
+        <v>0.935103817094359</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.8845984761544614</v>
+        <v>0.884673920460158</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.2033793401415985</v>
+        <v>0.202850597971508</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.331626</v>
+        <v>0.330816</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7621041.6</v>
+        <v>7638431.961538462</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1463091.527252</v>
+        <v>1461772.405828</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.007090098790202326</v>
+        <v>0.007127555721542105</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02881851247498287</v>
+        <v>0.02857905115243414</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>9252265</v>
+        <v>9720331</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>4576725.16585</v>
+        <v>4738720.92434</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">

--- a/downloads/精品货价监控指标_Sheet1.xlsx
+++ b/downloads/精品货价监控指标_Sheet1.xlsx
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C1" s="11" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         <v>71810000</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>56999284.90107001</v>
+        <v>59282290.94605001</v>
       </c>
       <c r="E6" s="104">
         <f>D6/C6</f>
         <v/>
       </c>
       <c r="F6" s="103" t="n">
-        <v>55034458.62962</v>
+        <v>57053880.82841</v>
       </c>
       <c r="G6" s="104">
         <f>D6/F6-1</f>
         <v/>
       </c>
       <c r="H6" s="103" t="n">
-        <v>60271461.32210948</v>
+        <v>62579169.06536008</v>
       </c>
       <c r="I6" s="104">
         <f>D6/H6</f>
         <v/>
       </c>
       <c r="J6" s="103" t="n">
-        <v>60500000</v>
+        <v>62600000</v>
       </c>
       <c r="K6" s="104">
         <f>D6/J6</f>
@@ -1884,28 +1884,28 @@
         <v>132000000</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>79575002.75239</v>
+        <v>82216567.05815001</v>
       </c>
       <c r="E7" s="104">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="103" t="n">
-        <v>88621756.21001998</v>
+        <v>91704524.86462997</v>
       </c>
       <c r="G7" s="104">
         <f>D7/F7-1</f>
         <v/>
       </c>
       <c r="H7" s="103" t="n">
-        <v>110790041.7005772</v>
+        <v>115032033.3745652</v>
       </c>
       <c r="I7" s="104">
         <f>D7/H7</f>
         <v/>
       </c>
       <c r="J7" s="103" t="n">
-        <v>111158802.7</v>
+        <v>115026097</v>
       </c>
       <c r="K7" s="104">
         <f>D7/J7</f>
@@ -1923,28 +1923,28 @@
         <v>9437018</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>9133109.288960002</v>
+        <v>9352880.30896</v>
       </c>
       <c r="E8" s="104">
         <f>D8/C8</f>
         <v/>
       </c>
       <c r="F8" s="103" t="n">
-        <v>6257675.0648</v>
+        <v>6429613.647990001</v>
       </c>
       <c r="G8" s="104">
         <f>D8/F8-1</f>
         <v/>
       </c>
       <c r="H8" s="103" t="n">
-        <v>7920663.770826501</v>
+        <v>8223934.617669493</v>
       </c>
       <c r="I8" s="104">
         <f>D8/H8</f>
         <v/>
       </c>
       <c r="J8" s="103" t="n">
-        <v>7997018.15389968</v>
+        <v>8257018.15389968</v>
       </c>
       <c r="K8" s="104">
         <f>D8/J8</f>
@@ -1962,28 +1962,28 @@
         <v>88000000</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>69431574.30306</v>
+        <v>72595270.08000998</v>
       </c>
       <c r="E9" s="104">
         <f>D9/C9</f>
         <v/>
       </c>
       <c r="F9" s="103" t="n">
-        <v>60801537.63507</v>
+        <v>63877686.13121</v>
       </c>
       <c r="G9" s="104">
         <f>D9/F9-1</f>
         <v/>
       </c>
       <c r="H9" s="103" t="n">
-        <v>73860027.80038483</v>
+        <v>76688022.24971017</v>
       </c>
       <c r="I9" s="104">
         <f>D9/H9</f>
         <v/>
       </c>
       <c r="J9" s="103" t="n">
-        <v>74144241</v>
+        <v>77541457</v>
       </c>
       <c r="K9" s="104">
         <f>D9/J9</f>
@@ -2001,28 +2001,28 @@
         <v>66000000</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>51610245.77668999</v>
+        <v>53355811.23975999</v>
       </c>
       <c r="E10" s="104">
         <f>D10/C10</f>
         <v/>
       </c>
       <c r="F10" s="103" t="n">
-        <v>45753281.23078001</v>
+        <v>47343676.45017999</v>
       </c>
       <c r="G10" s="104">
         <f>D10/F10-1</f>
         <v/>
       </c>
       <c r="H10" s="103" t="n">
-        <v>55395020.85028862</v>
+        <v>57516016.68728262</v>
       </c>
       <c r="I10" s="104">
         <f>D10/H10</f>
         <v/>
       </c>
       <c r="J10" s="103" t="n">
-        <v>56100000</v>
+        <v>57900000</v>
       </c>
       <c r="K10" s="104">
         <f>D10/J10</f>
@@ -2040,28 +2040,28 @@
         <v>62390797</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>39250344.41577</v>
+        <v>40718302.81533001</v>
       </c>
       <c r="E11" s="104">
         <f>D11/C11</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n">
-        <v>45520419.64603</v>
+        <v>47251904.58927</v>
       </c>
       <c r="G11" s="104">
         <f>D11/F11-1</f>
         <v/>
       </c>
       <c r="H11" s="103" t="n">
-        <v>52365750.01032007</v>
+        <v>54370759.41492216</v>
       </c>
       <c r="I11" s="104">
         <f>D11/H11</f>
         <v/>
       </c>
       <c r="J11" s="103" t="n">
-        <v>52859416.16000002</v>
+        <v>54654650.90000002</v>
       </c>
       <c r="K11" s="104">
         <f>D11/J11</f>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C46" s="107" t="n">
-        <v>116.38536</v>
+        <v>116.37252</v>
       </c>
       <c r="D46" s="108" t="n">
         <v>120</v>
@@ -3952,31 +3952,31 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.969878</v>
+        <v>0.969771</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.030122</v>
+        <v>0.030229</v>
       </c>
       <c r="H46" s="104" t="n">
-        <v>0.792257</v>
+        <v>0.793679</v>
       </c>
       <c r="I46" s="104" t="n">
-        <v>0.838044</v>
+        <v>0.840204</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>-4.5787</v>
+        <v>-4.6525</v>
       </c>
       <c r="K46" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L46" s="104" t="n">
-        <v>0.9810990000000001</v>
+        <v>0.981531</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0.868744</v>
+        <v>0.8709039999999999</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>11.2355</v>
+        <v>11.06270000000001</v>
       </c>
       <c r="O46" s="14" t="n">
         <v>-2</v>
@@ -3999,31 +3999,31 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.548602</v>
+        <v>0.552836</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.451398</v>
+        <v>0.447164</v>
       </c>
       <c r="H47" s="104" t="n">
-        <v>0.860413</v>
+        <v>0.862525</v>
       </c>
       <c r="I47" s="104" t="n">
-        <v>0.845364</v>
+        <v>0.844747</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>1.5049</v>
+        <v>1.7778</v>
       </c>
       <c r="K47" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L47" s="104" t="n">
-        <v>0.949968</v>
+        <v>0.949715</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0.876064</v>
+        <v>0.8754469999999999</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>7.3904</v>
+        <v>7.426800000000014</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>-2</v>
@@ -4046,31 +4046,31 @@
         <v>120</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.917855</v>
+        <v>0.918307</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.082145</v>
+        <v>0.081693</v>
       </c>
       <c r="H48" s="104" t="n">
-        <v>0.745633</v>
+        <v>0.7451410000000001</v>
       </c>
       <c r="I48" s="104" t="n">
-        <v>0.776695</v>
+        <v>0.776822</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>-3.1062</v>
+        <v>-3.1681</v>
       </c>
       <c r="K48" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L48" s="104" t="n">
-        <v>0.729692</v>
+        <v>0.727641</v>
       </c>
       <c r="M48" s="104" t="n">
-        <v>0.807395</v>
+        <v>0.8075219999999999</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>-7.770299999999992</v>
+        <v>-7.988099999999989</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>-2</v>
@@ -4084,40 +4084,40 @@
         </is>
       </c>
       <c r="C49" s="107" t="n">
-        <v>87.87192760000001</v>
+        <v>87.086004192</v>
       </c>
       <c r="D49" s="108" t="n">
-        <v>100.37</v>
+        <v>99.396</v>
       </c>
       <c r="E49" s="108" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.87548</v>
+        <v>0.876152</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.12452</v>
+        <v>0.123848</v>
       </c>
       <c r="H49" s="104" t="n">
-        <v>0.809492</v>
+        <v>0.809742</v>
       </c>
       <c r="I49" s="104" t="n">
-        <v>0.829677</v>
+        <v>0.82944</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>-2.0185</v>
+        <v>-1.9698</v>
       </c>
       <c r="K49" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L49" s="104" t="n">
-        <v>0.86995</v>
+        <v>0.869915</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0.8603769999999998</v>
+        <v>0.8601399999999999</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>0.9573000000000178</v>
+        <v>0.9775000000000063</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>-2</v>
@@ -4140,31 +4140,31 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.819715</v>
+        <v>0.819269</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.180285</v>
+        <v>0.180731</v>
       </c>
       <c r="H50" s="104" t="n">
-        <v>0.887647</v>
+        <v>0.888065</v>
       </c>
       <c r="I50" s="104" t="n">
-        <v>0.835376</v>
+        <v>0.8355320000000001</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>5.2271</v>
+        <v>5.2533</v>
       </c>
       <c r="K50" s="109" t="n">
         <v>-2</v>
       </c>
       <c r="L50" s="104" t="n">
-        <v>0.886501</v>
+        <v>0.886522</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0.866076</v>
+        <v>0.866232</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2.042500000000004</v>
+        <v>2.028999999999996</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>-2</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.9397703933271144</v>
+        <v>0.9400170376200739</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.9279951388178347</v>
+        <v>0.9278937175607233</v>
       </c>
       <c r="E69" s="10">
         <f>D69-C69</f>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.9301326499269785</v>
+        <v>0.9295969216394627</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.8892783347494847</v>
+        <v>0.8888186180667089</v>
       </c>
       <c r="E70" s="10">
         <f>D70-C70</f>
@@ -6975,10 +6975,10 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.922493958562407</v>
+        <v>0.9219400076214633</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.8914821215654777</v>
+        <v>0.8912389392578917</v>
       </c>
       <c r="E71" s="10">
         <f>D71-C71</f>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.9792712353493512</v>
+        <v>0.9795473206723364</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.8798879221523218</v>
+        <v>0.8805529419547967</v>
       </c>
       <c r="E72" s="10">
         <f>D72-C72</f>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.9459716828904183</v>
+        <v>0.9444891078667765</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.8280673271363532</v>
+        <v>0.8272107325994765</v>
       </c>
       <c r="E73" s="10">
         <f>D73-C73</f>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.9405248187055548</v>
+        <v>0.9397490986296675</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.8791349788351291</v>
+        <v>0.8790686129160361</v>
       </c>
       <c r="E74" s="10">
         <f>D74-C74</f>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.935103817094359</v>
+        <v>0.9345430954304992</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.884673920460158</v>
+        <v>0.8844281210841539</v>
       </c>
       <c r="E75" s="10">
         <f>D75-C75</f>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C149" s="116" t="n">
-        <v>0.202850597971508</v>
+        <v>0.2025752109475947</v>
       </c>
       <c r="D149" s="116" t="n">
-        <v>0.330816</v>
+        <v>0.330517</v>
       </c>
       <c r="E149" s="20">
         <f>D149/C149</f>
@@ -10800,10 +10800,10 @@
         <v/>
       </c>
       <c r="I149" s="106" t="n">
-        <v>7638431.961538462</v>
+        <v>7636188.037037037</v>
       </c>
       <c r="J149" s="106" t="n">
-        <v>1461772.405828</v>
+        <v>1458008.503465</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C150" s="116" t="n">
-        <v>0.007127555721542105</v>
+        <v>0.007295338151612621</v>
       </c>
       <c r="D150" s="116" t="n">
-        <v>0.02857905115243414</v>
+        <v>0.02866368692945488</v>
       </c>
       <c r="E150" s="20">
         <f>D150/C150</f>
@@ -10839,10 +10839,10 @@
         <v/>
       </c>
       <c r="I150" s="106" t="n">
-        <v>9720331</v>
+        <v>10340122</v>
       </c>
       <c r="J150" s="106" t="n">
-        <v>4738720.92434</v>
+        <v>4918687.94053</v>
       </c>
     </row>
     <row r="152" ht="13.5" customHeight="1">
